--- a/data/rateBuildUp/File1/RPT_RPT9892372453518NR_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT9892372453518NR_rateBuildUp.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="29920" windowHeight="18760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RateBuildUp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RateBuildUp" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2964,10 +2964,10 @@
         <v>24089.16055757216</v>
       </c>
       <c r="F11" s="368" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="G11" s="370" t="n">
-        <v>22576.04277835389</v>
+        <v>22576.04277835388</v>
       </c>
       <c r="H11" s="371" t="n">
         <v>166.5224209154689</v>
@@ -2979,7 +2979,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="K11" s="372" t="n">
-        <v>176.3444366910916</v>
+        <v>176.3444366910915</v>
       </c>
       <c r="L11" s="373" t="n">
         <v>183.9927999942387</v>
@@ -2994,10 +2994,10 @@
         <v>103.2815800451463</v>
       </c>
       <c r="P11" s="372" t="n">
-        <v>93.68583900106417</v>
+        <v>93.68583900106414</v>
       </c>
       <c r="Q11" s="373" t="n">
-        <v>89.87200575626353</v>
+        <v>89.87200575626352</v>
       </c>
       <c r="S11" s="72" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         <v>24089.16055757216</v>
       </c>
       <c r="W11" s="375" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="X11" s="376" t="n">
-        <v>22576.04277835389</v>
+        <v>22576.04277835388</v>
       </c>
       <c r="Y11" s="377" t="n">
         <v>166.5224209154689</v>
@@ -3029,7 +3029,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="AB11" s="372" t="n">
-        <v>176.3444366910916</v>
+        <v>176.3444366910915</v>
       </c>
       <c r="AC11" s="378" t="n">
         <v>183.9927999942387</v>
@@ -3044,10 +3044,10 @@
         <v>103.2815800451463</v>
       </c>
       <c r="AG11" s="372" t="n">
-        <v>93.68583900106417</v>
+        <v>93.68583900106414</v>
       </c>
       <c r="AH11" s="378" t="n">
-        <v>89.87200575626353</v>
+        <v>89.87200575626352</v>
       </c>
       <c r="AJ11" s="78" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         <v>24089.16055757216</v>
       </c>
       <c r="AN11" s="368" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="AO11" s="380" t="n">
-        <v>22576.04277835389</v>
+        <v>22576.04277835388</v>
       </c>
       <c r="AP11" s="381" t="n">
         <v>166.5224209154689</v>
@@ -3079,7 +3079,7 @@
         <v>177.8294739110173</v>
       </c>
       <c r="AS11" s="372" t="n">
-        <v>176.3444366910916</v>
+        <v>176.3444366910915</v>
       </c>
       <c r="AT11" s="382" t="n">
         <v>183.9927999942387</v>
@@ -3094,10 +3094,10 @@
         <v>103.2815799610111</v>
       </c>
       <c r="AX11" s="372" t="n">
-        <v>93.68583890529057</v>
+        <v>93.68583890529054</v>
       </c>
       <c r="AY11" s="382" t="n">
-        <v>89.87200586001615</v>
+        <v>89.87200586001613</v>
       </c>
       <c r="BA11" s="83" t="inlineStr">
         <is>
@@ -3108,13 +3108,13 @@
         <v>26351.48216982734</v>
       </c>
       <c r="BC11" s="384" t="n">
-        <v>25038.33755863324</v>
+        <v>25038.33755863325</v>
       </c>
       <c r="BD11" s="384" t="n">
         <v>26645.81401887292</v>
       </c>
       <c r="BE11" s="384" t="n">
-        <v>26010.40830801733</v>
+        <v>26010.40830801734</v>
       </c>
       <c r="BF11" s="385" t="n">
         <v>26274.64259933642</v>
@@ -3155,28 +3155,28 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>26203.1072757299</v>
+        <v>26203.10727572989</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>24936.17960454477</v>
+        <v>24936.17960454476</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>26611.64391549987</v>
+        <v>26611.64391549986</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>26028.90500448929</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26365.14279158321</v>
+        <v>26365.1427915832</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>171.8792907918565</v>
+        <v>171.8792907918564</v>
       </c>
       <c r="BY11" s="372" t="n">
         <v>179.2220110803922</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>195.907882372609</v>
+        <v>195.9078823726089</v>
       </c>
       <c r="CA11" s="372" t="n">
         <v>199.3146296083648</v>
@@ -3185,7 +3185,7 @@
         <v>213.1926627868784</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>156.0446733835886</v>
+        <v>156.0446733835885</v>
       </c>
       <c r="CD11" s="389" t="n">
         <v>129.1940920210261</v>
@@ -3197,22 +3197,22 @@
         <v>106.6766058230473</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>105.1818718247416</v>
+        <v>105.1818718247415</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>0.6389788461903265</v>
+        <v>0.6389788461904118</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>0.7625478833641637</v>
+        <v>0.7625478833642205</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>0.7951566387490345</v>
+        <v>0.7951566387490914</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>0.8866823740377185</v>
+        <v>0.886682374037747</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>0.9434065040171333</v>
+        <v>0.9434065040171902</v>
       </c>
       <c r="DC11" s="393" t="n">
         <v>0.007228790260420208</v>
@@ -3221,13 +3221,13 @@
         <v>0.007628852866560994</v>
       </c>
       <c r="DE11" s="394" t="n">
-        <v>0.007522316429608733</v>
+        <v>0.007522316429608734</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.008028176757755748</v>
+        <v>0.00802817675775575</v>
       </c>
       <c r="DG11" s="395" t="n">
-        <v>0.008141014872206941</v>
+        <v>0.008141014872206942</v>
       </c>
     </row>
     <row r="12">
@@ -3446,10 +3446,10 @@
         <v>25611.23615751466</v>
       </c>
       <c r="BV12" s="375" t="n">
-        <v>29739.34091087101</v>
+        <v>29739.340910871</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>33081.47916846323</v>
+        <v>33081.47916846322</v>
       </c>
       <c r="BX12" s="386" t="n">
         <v>272.3350931926751</v>
@@ -3461,7 +3461,7 @@
         <v>310.485521541103</v>
       </c>
       <c r="CA12" s="372" t="n">
-        <v>346.3989019796252</v>
+        <v>346.3989019796251</v>
       </c>
       <c r="CB12" s="387" t="n">
         <v>372.3484651943247</v>
@@ -3479,10 +3479,10 @@
         <v>186.4227432420769</v>
       </c>
       <c r="CG12" s="387" t="n">
-        <v>197.2957607538008</v>
+        <v>197.2957607538007</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>0.6589594238606651</v>
+        <v>0.6589594238607219</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>0.7030155109170551</v>
@@ -3491,10 +3491,10 @@
         <v>0.7452609770264189</v>
       </c>
       <c r="CZ12" s="103" t="n">
-        <v>0.7830932479166108</v>
+        <v>0.7830932479166677</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>0.652173448622591</v>
+        <v>0.6521734486226478</v>
       </c>
       <c r="DC12" s="396" t="n">
         <v>0.002321834056615353</v>
@@ -3522,7 +3522,7 @@
         <v>41964.6638218786</v>
       </c>
       <c r="D13" s="368" t="n">
-        <v>47358.56763505709</v>
+        <v>47358.56763505708</v>
       </c>
       <c r="E13" s="368" t="n">
         <v>56366.24695023875</v>
@@ -3537,7 +3537,7 @@
         <v>540.4169897062984</v>
       </c>
       <c r="I13" s="372" t="n">
-        <v>585.4161049931174</v>
+        <v>585.4161049931173</v>
       </c>
       <c r="J13" s="372" t="n">
         <v>675.1286623780476</v>
@@ -3552,7 +3552,7 @@
         <v>445.4926848525594</v>
       </c>
       <c r="N13" s="372" t="n">
-        <v>432.4847715283257</v>
+        <v>432.4847715283256</v>
       </c>
       <c r="O13" s="372" t="n">
         <v>441.0227177832657</v>
@@ -3572,7 +3572,7 @@
         <v>41964.6638218786</v>
       </c>
       <c r="U13" s="375" t="n">
-        <v>47358.56763505709</v>
+        <v>47358.56763505708</v>
       </c>
       <c r="V13" s="375" t="n">
         <v>56366.24695023875</v>
@@ -3587,7 +3587,7 @@
         <v>540.4169897062984</v>
       </c>
       <c r="Z13" s="372" t="n">
-        <v>585.4161049931174</v>
+        <v>585.4161049931173</v>
       </c>
       <c r="AA13" s="372" t="n">
         <v>675.1286623780476</v>
@@ -3602,7 +3602,7 @@
         <v>445.4926848525594</v>
       </c>
       <c r="AE13" s="372" t="n">
-        <v>432.4847715283257</v>
+        <v>432.4847715283256</v>
       </c>
       <c r="AF13" s="372" t="n">
         <v>441.0227177832657</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>42877.82934545783</v>
+        <v>42877.82934545782</v>
       </c>
       <c r="AL13" s="368" t="n">
         <v>47741.35846094236</v>
@@ -3634,7 +3634,7 @@
         <v>76472.16975908712</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>561.3081632890123</v>
+        <v>561.3081632890122</v>
       </c>
       <c r="AQ13" s="372" t="n">
         <v>602.8201312928923</v>
@@ -3672,7 +3672,7 @@
         <v>44223.82099271537</v>
       </c>
       <c r="BC13" s="384" t="n">
-        <v>50720.40302179554</v>
+        <v>50720.40302179555</v>
       </c>
       <c r="BD13" s="384" t="n">
         <v>62177.51503362879</v>
@@ -3681,7 +3681,7 @@
         <v>77060.78327347637</v>
       </c>
       <c r="BF13" s="385" t="n">
-        <v>88527.19202416009</v>
+        <v>88527.1920241601</v>
       </c>
       <c r="BG13" s="386" t="n">
         <v>578.9283672698959</v>
@@ -3696,13 +3696,13 @@
         <v>962.6600777565143</v>
       </c>
       <c r="BK13" s="387" t="n">
-        <v>1055.539724299017</v>
+        <v>1055.539724299018</v>
       </c>
       <c r="BL13" s="386" t="n">
         <v>475.857275011304</v>
       </c>
       <c r="BM13" s="372" t="n">
-        <v>470.4922353916562</v>
+        <v>470.4922353916563</v>
       </c>
       <c r="BN13" s="372" t="n">
         <v>493.1278604947497</v>
@@ -3711,7 +3711,7 @@
         <v>562.0140619373698</v>
       </c>
       <c r="BP13" s="387" t="n">
-        <v>581.7162805798678</v>
+        <v>581.7162805798679</v>
       </c>
       <c r="BR13" s="111" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>77683.36857055586</v>
       </c>
       <c r="BW13" s="392" t="n">
-        <v>89449.62510033298</v>
+        <v>89449.625100333</v>
       </c>
       <c r="BX13" s="386" t="n">
         <v>579.1549261281195</v>
@@ -3761,7 +3761,7 @@
         <v>566.8663642518962</v>
       </c>
       <c r="CG13" s="387" t="n">
-        <v>588.0672647234338</v>
+        <v>588.0672647234339</v>
       </c>
       <c r="CW13" s="102" t="n">
         <v>-0.2265588582235978</v>
@@ -3779,10 +3779,10 @@
         <v>-0.4455219254839449</v>
       </c>
       <c r="DC13" s="396" t="n">
-        <v>0.0003617448861470029</v>
+        <v>0.000361744886147003</v>
       </c>
       <c r="DD13" s="397" t="n">
-        <v>0.000336695107287859</v>
+        <v>0.0003366951072878591</v>
       </c>
       <c r="DE13" s="397" t="n">
         <v>0.0002838395284740453</v>
@@ -4001,64 +4001,64 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702485</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="BW14" s="421" t="n">
         <v>1052.062863383992</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="BY14" s="417" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>379.891773714928</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="CB14" s="418" t="n">
-        <v>441.6747640809031</v>
+        <v>441.6747640809029</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>229.300384964129</v>
+        <v>229.3003849641289</v>
       </c>
       <c r="CD14" s="417" t="n">
-        <v>347.2212936759051</v>
+        <v>347.221293675905</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>379.891773714928</v>
+        <v>379.8917737149279</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>410.1189307766605</v>
+        <v>410.1189307766604</v>
       </c>
       <c r="CG14" s="418" t="n">
-        <v>441.6747640809031</v>
+        <v>441.6747640809029</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>0.9305820627104993</v>
+        <v>0.9305820627105277</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>1.130560236970041</v>
+        <v>1.130560236970211</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>1.236935640543891</v>
+        <v>1.236935640544004</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>1.33535588694599</v>
+        <v>1.335355886946104</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>1.438102430218805</v>
+        <v>1.438102430218976</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>89578.8610874349</v>
       </c>
       <c r="D15" s="425" t="n">
-        <v>92053.67536447017</v>
+        <v>92053.67536447014</v>
       </c>
       <c r="E15" s="425" t="n">
         <v>104426.6418198824</v>
@@ -4101,7 +4101,7 @@
         <v>281.6458707547292</v>
       </c>
       <c r="I15" s="427" t="n">
-        <v>301.8521807615509</v>
+        <v>301.8521807615508</v>
       </c>
       <c r="J15" s="427" t="n">
         <v>340.8945737987179</v>
@@ -4116,7 +4116,7 @@
         <v>239.222461375002</v>
       </c>
       <c r="N15" s="427" t="n">
-        <v>211.8499084764852</v>
+        <v>211.8499084764851</v>
       </c>
       <c r="O15" s="427" t="n">
         <v>203.5030310354896</v>
@@ -4136,7 +4136,7 @@
         <v>89578.8610874349</v>
       </c>
       <c r="U15" s="430" t="n">
-        <v>92053.67536447017</v>
+        <v>92053.67536447014</v>
       </c>
       <c r="V15" s="430" t="n">
         <v>104426.6418198824</v>
@@ -4151,7 +4151,7 @@
         <v>281.6458707547292</v>
       </c>
       <c r="Z15" s="433" t="n">
-        <v>301.8521807615509</v>
+        <v>301.8521807615508</v>
       </c>
       <c r="AA15" s="433" t="n">
         <v>340.8945737987179</v>
@@ -4166,7 +4166,7 @@
         <v>239.222461375002</v>
       </c>
       <c r="AE15" s="433" t="n">
-        <v>211.8499084764852</v>
+        <v>211.8499084764851</v>
       </c>
       <c r="AF15" s="433" t="n">
         <v>203.5030310354896</v>
@@ -4204,13 +4204,13 @@
         <v>307.9414533823692</v>
       </c>
       <c r="AR15" s="437" t="n">
-        <v>347.3855163222884</v>
+        <v>347.3855163222883</v>
       </c>
       <c r="AS15" s="437" t="n">
         <v>397.3595148844121</v>
       </c>
       <c r="AT15" s="438" t="n">
-        <v>431.9621397489195</v>
+        <v>431.9621397489194</v>
       </c>
       <c r="AU15" s="437" t="n">
         <v>242.479117894165</v>
@@ -4225,7 +4225,7 @@
         <v>217.42376895703</v>
       </c>
       <c r="AY15" s="438" t="n">
-        <v>223.5961438609552</v>
+        <v>223.5961438609551</v>
       </c>
       <c r="BA15" s="155" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>93448.66435652964</v>
+        <v>93448.66435652963</v>
       </c>
       <c r="BT15" s="440" t="n">
         <v>98663.05884628771</v>
@@ -4301,7 +4301,7 @@
         <v>297.9288864996687</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>328.0617592449053</v>
+        <v>328.0617592449052</v>
       </c>
       <c r="BZ15" s="443" t="n">
         <v>381.8221680697479</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>9.473945063523479</v>
+        <v>9.473945063523475</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>0</v>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="BX29" s="386" t="n">
-        <v>0.06214434575962197</v>
+        <v>0.06214434575962194</v>
       </c>
       <c r="BY29" s="372" t="n">
         <v>0</v>
@@ -7366,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="CC29" s="388" t="n">
-        <v>0.05641921194822884</v>
+        <v>0.05641921194822882</v>
       </c>
       <c r="CD29" s="389" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-0.0002198705315343621</v>
+        <v>-0.0002198705315343344</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0</v>
@@ -9382,7 +9382,7 @@
         <v>70.62874672220298</v>
       </c>
       <c r="BD38" s="375" t="n">
-        <v>32.45283468400486</v>
+        <v>32.45283468400487</v>
       </c>
       <c r="BE38" s="375" t="n">
         <v>14.61425526447144</v>
@@ -9397,7 +9397,7 @@
         <v>0.5077047866772376</v>
       </c>
       <c r="BI38" s="372" t="n">
-        <v>0.2395712588234515</v>
+        <v>0.2395712588234516</v>
       </c>
       <c r="BJ38" s="372" t="n">
         <v>0.1124854728516923</v>
@@ -9412,7 +9412,7 @@
         <v>0.3648704141517646</v>
       </c>
       <c r="BN38" s="389" t="n">
-        <v>0.1391405911537223</v>
+        <v>0.1391405911537224</v>
       </c>
       <c r="BO38" s="389" t="n">
         <v>0.05975972980213357</v>
@@ -9426,13 +9426,13 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>128.5810065561253</v>
+        <v>128.5810065561252</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.62983584535287</v>
+        <v>70.62983584535286</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>32.41792684373758</v>
+        <v>32.41792684373759</v>
       </c>
       <c r="BV38" s="375" t="n">
         <v>14.4970939585562</v>
@@ -9441,49 +9441,49 @@
         <v>15.94387757167488</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.8434271547878568</v>
+        <v>0.8434271547878563</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.5076327417923732</v>
+        <v>0.5076327417923731</v>
       </c>
       <c r="BZ38" s="372" t="n">
         <v>0.2386522012331492</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.1110105443255848</v>
+        <v>0.1110105443255847</v>
       </c>
       <c r="CB38" s="387" t="n">
         <v>0.1289246844412498</v>
       </c>
       <c r="CC38" s="388" t="n">
-        <v>0.7657252615214785</v>
+        <v>0.7657252615214781</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>0.3659324586341772</v>
+        <v>0.3659324586341771</v>
       </c>
       <c r="CE38" s="389" t="n">
         <v>0.1393239773741763</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.059414745934562</v>
+        <v>0.05941474593456197</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.06360697153776257</v>
+        <v>0.06360697153776255</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-8.508016421049369e-06</v>
+        <v>-8.50801642060528e-06</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>7.204488486445282e-05</v>
+        <v>7.204488486456384e-05</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>0.0009190575903023634</v>
+        <v>0.0009190575903024467</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>0.001474928526107533</v>
+        <v>0.001474928526107575</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>0.001695023682283581</v>
+        <v>0.001695023682283608</v>
       </c>
       <c r="DC38" s="393" t="n">
         <v>0.003528009884850775</v>
@@ -9670,7 +9670,7 @@
         <v>84.04164482688768</v>
       </c>
       <c r="BF39" s="392" t="n">
-        <v>91.85091082748846</v>
+        <v>91.85091082748843</v>
       </c>
       <c r="BG39" s="386" t="n">
         <v>1.546065453660562</v>
@@ -9685,7 +9685,7 @@
         <v>0.9870981007482287</v>
       </c>
       <c r="BK39" s="387" t="n">
-        <v>1.044789313442234</v>
+        <v>1.044789313442233</v>
       </c>
       <c r="BL39" s="386" t="n">
         <v>1.160510009734086</v>
@@ -9700,7 +9700,7 @@
         <v>0.5265382695363803</v>
       </c>
       <c r="BP39" s="387" t="n">
-        <v>0.5475500037704478</v>
+        <v>0.5475500037704476</v>
       </c>
       <c r="BR39" s="101" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>82.71716419582476</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>90.58922323081408</v>
+        <v>90.58922323081407</v>
       </c>
       <c r="BX39" s="386" t="n">
         <v>1.527013027016195</v>
@@ -9750,10 +9750,10 @@
         <v>0.5185172297128533</v>
       </c>
       <c r="CG39" s="387" t="n">
-        <v>0.5402681549517188</v>
+        <v>0.5402681549517186</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.01905242664436702</v>
+        <v>0.01905242664436724</v>
       </c>
       <c r="CX39" s="103" t="n">
         <v>0.02052004249823236</v>
@@ -9967,7 +9967,7 @@
         <v>2.400774093376043</v>
       </c>
       <c r="BK40" s="387" t="n">
-        <v>4.113416937050489</v>
+        <v>4.113416937050488</v>
       </c>
       <c r="BL40" s="386" t="n">
         <v>0.5603194807761371</v>
@@ -9976,7 +9976,7 @@
         <v>0.7101505215997633</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>0.8864721134473434</v>
+        <v>0.8864721134473437</v>
       </c>
       <c r="BO40" s="372" t="n">
         <v>1.401604607055853</v>
@@ -10002,7 +10002,7 @@
         <v>192.7906562953858</v>
       </c>
       <c r="BW40" s="392" t="n">
-        <v>347.5611327190496</v>
+        <v>347.5611327190495</v>
       </c>
       <c r="BX40" s="386" t="n">
         <v>0.6733796218804903</v>
@@ -10017,7 +10017,7 @@
         <v>2.390163817245793</v>
       </c>
       <c r="CB40" s="387" t="n">
-        <v>4.103085148771919</v>
+        <v>4.103085148771918</v>
       </c>
       <c r="CC40" s="386" t="n">
         <v>0.5547423026400453</v>
@@ -10026,13 +10026,13 @@
         <v>0.7058546822306386</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>0.8851035230875919</v>
+        <v>0.8851035230875922</v>
       </c>
       <c r="CF40" s="372" t="n">
         <v>1.406820280928509</v>
       </c>
       <c r="CG40" s="387" t="n">
-        <v>2.284965693405785</v>
+        <v>2.284965693405784</v>
       </c>
       <c r="CW40" s="102" t="n">
         <v>0.008305537072977653</v>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="BV41" s="420" t="n">
-        <v>82.54761814889748</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="BZ41" s="417" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236776</v>
       </c>
       <c r="CB41" s="418" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>22.52427460963667</v>
+        <v>22.52427460963666</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>32.52028395838352</v>
+        <v>32.52028395838351</v>
       </c>
       <c r="CE41" s="417" t="n">
         <v>33.86831783406382</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>35.35776816236777</v>
+        <v>35.35776816236776</v>
       </c>
       <c r="CG41" s="418" t="n">
-        <v>36.92500467223028</v>
+        <v>36.92500467223027</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.09141147290516471</v>
+        <v>0.09141147290517182</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.1058867661861811</v>
+        <v>0.1058867661861953</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.1102759583461221</v>
+        <v>0.1102759583461292</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.1151256387396629</v>
+        <v>0.11512563873967</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.1202286009377929</v>
+        <v>0.1202286009378071</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10357,7 +10357,7 @@
         <v>386.8777943689183</v>
       </c>
       <c r="D42" s="425" t="n">
-        <v>306.289957259815</v>
+        <v>306.2899572598151</v>
       </c>
       <c r="E42" s="425" t="n">
         <v>326.7226368891187</v>
@@ -10387,7 +10387,7 @@
         <v>1.03316627490865</v>
       </c>
       <c r="N42" s="427" t="n">
-        <v>0.7048876555536522</v>
+        <v>0.7048876555536524</v>
       </c>
       <c r="O42" s="427" t="n">
         <v>0.6367057846169684</v>
@@ -10407,7 +10407,7 @@
         <v>386.8777943689183</v>
       </c>
       <c r="U42" s="430" t="n">
-        <v>306.289957259815</v>
+        <v>306.2899572598151</v>
       </c>
       <c r="V42" s="430" t="n">
         <v>326.7226368891187</v>
@@ -10437,7 +10437,7 @@
         <v>1.03316627490865</v>
       </c>
       <c r="AE42" s="433" t="n">
-        <v>0.7048876555536522</v>
+        <v>0.7048876555536524</v>
       </c>
       <c r="AF42" s="433" t="n">
         <v>0.6367057846169684</v>
@@ -10507,7 +10507,7 @@
         <v>375.0160259739762</v>
       </c>
       <c r="BC42" s="440" t="n">
-        <v>288.1847568729067</v>
+        <v>288.1847568729066</v>
       </c>
       <c r="BD42" s="440" t="n">
         <v>299.0010333103696</v>
@@ -10516,28 +10516,28 @@
         <v>373.8923983895505</v>
       </c>
       <c r="BF42" s="441" t="n">
-        <v>541.3620711002279</v>
+        <v>541.3620711002278</v>
       </c>
       <c r="BG42" s="442" t="n">
-        <v>1.195330134541267</v>
+        <v>1.195330134541268</v>
       </c>
       <c r="BH42" s="443" t="n">
-        <v>0.9600543652473262</v>
+        <v>0.960054365247326</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>0.9917181252510245</v>
+        <v>0.9917181252510243</v>
       </c>
       <c r="BJ42" s="443" t="n">
         <v>1.256981514897622</v>
       </c>
       <c r="BK42" s="444" t="n">
-        <v>1.823553892449678</v>
+        <v>1.823553892449677</v>
       </c>
       <c r="BL42" s="443" t="n">
         <v>1.004879198531257</v>
       </c>
       <c r="BM42" s="443" t="n">
-        <v>0.6658266572964089</v>
+        <v>0.6658266572964088</v>
       </c>
       <c r="BN42" s="443" t="n">
         <v>0.5846425497588634</v>
@@ -10546,7 +10546,7 @@
         <v>0.6877843570899709</v>
       </c>
       <c r="BP42" s="444" t="n">
-        <v>0.9439244344686875</v>
+        <v>0.9439244344686872</v>
       </c>
       <c r="BR42" s="155" t="inlineStr">
         <is>
@@ -10554,34 +10554,34 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>372.4189745924095</v>
+        <v>372.4189745924094</v>
       </c>
       <c r="BT42" s="440" t="n">
         <v>285.8482213177363</v>
       </c>
       <c r="BU42" s="440" t="n">
-        <v>296.8857346669485</v>
+        <v>296.8857346669486</v>
       </c>
       <c r="BV42" s="440" t="n">
         <v>372.5525325986642</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>542.0490575350248</v>
+        <v>542.0490575350246</v>
       </c>
       <c r="BX42" s="442" t="n">
         <v>1.187329655010871</v>
       </c>
       <c r="BY42" s="443" t="n">
-        <v>0.9504658730338159</v>
+        <v>0.9504658730338157</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>0.9804288971651031</v>
+        <v>0.9804288971651034</v>
       </c>
       <c r="CA42" s="443" t="n">
         <v>1.244165984092921</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>1.809225069629854</v>
+        <v>1.809225069629853</v>
       </c>
       <c r="CC42" s="443" t="n">
         <v>1.00010075122926</v>
@@ -10590,13 +10590,13 @@
         <v>0.6615315899007601</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>0.5813276294704893</v>
+        <v>0.5813276294704895</v>
       </c>
       <c r="CF42" s="443" t="n">
         <v>0.6862277568899726</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>0.9462704602308021</v>
+        <v>0.9462704602308019</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11240,10 +11240,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="E47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="F47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="G47" s="455" t="n">
         <v>22594.86520251621</v>
@@ -11258,7 +11258,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="K47" s="372" t="n">
-        <v>176.4728096596965</v>
+        <v>176.4728096596964</v>
       </c>
       <c r="L47" s="373" t="n">
         <v>184.1462011265056</v>
@@ -11273,10 +11273,10 @@
         <v>103.4371137297133</v>
       </c>
       <c r="P47" s="372" t="n">
-        <v>93.75403922044434</v>
+        <v>93.75403922044431</v>
       </c>
       <c r="Q47" s="373" t="n">
-        <v>89.94693514177503</v>
+        <v>89.94693514177501</v>
       </c>
       <c r="S47" s="72" t="inlineStr">
         <is>
@@ -11290,10 +11290,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="V47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="W47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="X47" s="376" t="n">
         <v>22594.86520251621</v>
@@ -11308,7 +11308,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="AB47" s="372" t="n">
-        <v>176.4728096596965</v>
+        <v>176.4728096596964</v>
       </c>
       <c r="AC47" s="378" t="n">
         <v>184.1462011265056</v>
@@ -11323,10 +11323,10 @@
         <v>103.4371137297133</v>
       </c>
       <c r="AG47" s="372" t="n">
-        <v>93.75403922044434</v>
+        <v>93.75403922044431</v>
       </c>
       <c r="AH47" s="378" t="n">
-        <v>89.94693514177503</v>
+        <v>89.94693514177501</v>
       </c>
       <c r="AJ47" s="78" t="inlineStr">
         <is>
@@ -11340,10 +11340,10 @@
         <v>23420.69497879438</v>
       </c>
       <c r="AM47" s="375" t="n">
-        <v>24125.43688001037</v>
+        <v>24125.43688001036</v>
       </c>
       <c r="AN47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="AO47" s="456" t="n">
         <v>22594.86520251621</v>
@@ -11358,7 +11358,7 @@
         <v>178.0972706787459</v>
       </c>
       <c r="AS47" s="372" t="n">
-        <v>176.4728096596965</v>
+        <v>176.4728096596964</v>
       </c>
       <c r="AT47" s="382" t="n">
         <v>184.1462011265056</v>
@@ -11373,10 +11373,10 @@
         <v>103.4371136454514</v>
       </c>
       <c r="AX47" s="372" t="n">
-        <v>93.75403912460102</v>
+        <v>93.75403912460099</v>
       </c>
       <c r="AY47" s="382" t="n">
-        <v>89.94693524561416</v>
+        <v>89.94693524561414</v>
       </c>
       <c r="BA47" s="83" t="inlineStr">
         <is>
@@ -11390,10 +11390,10 @@
         <v>25108.96630535545</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>26678.26685355693</v>
+        <v>26678.26685355692</v>
       </c>
       <c r="BE47" s="375" t="n">
-        <v>26025.0225632818</v>
+        <v>26025.02256328181</v>
       </c>
       <c r="BF47" s="392" t="n">
         <v>26290.6697271283</v>
@@ -11408,7 +11408,7 @@
         <v>196.9426102701814</v>
       </c>
       <c r="BJ47" s="372" t="n">
-        <v>200.3137974552542</v>
+        <v>200.3137974552543</v>
       </c>
       <c r="BK47" s="387" t="n">
         <v>214.2666889990191</v>
@@ -11434,43 +11434,43 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>26341.16222734955</v>
+        <v>26341.16222734954</v>
       </c>
       <c r="BT47" s="375" t="n">
         <v>25006.80944039012</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>26644.06184234361</v>
+        <v>26644.0618423436</v>
       </c>
       <c r="BV47" s="375" t="n">
         <v>26043.40209844784</v>
       </c>
       <c r="BW47" s="392" t="n">
-        <v>26381.08666915488</v>
+        <v>26381.08666915487</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>172.784862292404</v>
+        <v>172.7848622924039</v>
       </c>
       <c r="BY47" s="372" t="n">
         <v>179.7296438221846</v>
       </c>
       <c r="BZ47" s="372" t="n">
-        <v>196.1465345738421</v>
+        <v>196.146534573842</v>
       </c>
       <c r="CA47" s="372" t="n">
         <v>199.4256401526904</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>213.3215874713197</v>
+        <v>213.3215874713196</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>156.8668178570583</v>
+        <v>156.8668178570582</v>
       </c>
       <c r="CD47" s="389" t="n">
         <v>129.5600244796603</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>114.5093789363011</v>
+        <v>114.509378936301</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>106.7360205689818</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>22432.76645581946</v>
+        <v>22432.76645581945</v>
       </c>
       <c r="BT48" s="375" t="n">
         <v>22124.62439179996</v>
@@ -11695,10 +11695,10 @@
         <v>25686.67107992767</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>29822.05807506683</v>
+        <v>29822.05807506682</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>33172.06839169404</v>
+        <v>33172.06839169403</v>
       </c>
       <c r="BX48" s="386" t="n">
         <v>274.532950600186</v>
@@ -11710,13 +11710,13 @@
         <v>311.4000205947125</v>
       </c>
       <c r="CA48" s="372" t="n">
-        <v>347.3623777653925</v>
+        <v>347.3623777653924</v>
       </c>
       <c r="CB48" s="387" t="n">
-        <v>373.3680918579745</v>
+        <v>373.3680918579744</v>
       </c>
       <c r="CC48" s="386" t="n">
-        <v>206.5575802734972</v>
+        <v>206.5575802734971</v>
       </c>
       <c r="CD48" s="372" t="n">
         <v>171.3234454341575</v>
@@ -11725,10 +11725,10 @@
         <v>171.5625909330092</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>186.9412604717898</v>
+        <v>186.9412604717897</v>
       </c>
       <c r="CG48" s="387" t="n">
-        <v>197.8360289087525</v>
+        <v>197.8360289087524</v>
       </c>
     </row>
     <row r="49">
@@ -11741,7 +11741,7 @@
         <v>42018.37945735098</v>
       </c>
       <c r="D49" s="375" t="n">
-        <v>47439.95465122465</v>
+        <v>47439.95465122464</v>
       </c>
       <c r="E49" s="375" t="n">
         <v>56489.12845072968</v>
@@ -11756,7 +11756,7 @@
         <v>541.1087346025606</v>
       </c>
       <c r="I49" s="372" t="n">
-        <v>586.4221588579423</v>
+        <v>586.4221588579422</v>
       </c>
       <c r="J49" s="372" t="n">
         <v>676.6004797784625</v>
@@ -11791,7 +11791,7 @@
         <v>42018.37945735098</v>
       </c>
       <c r="U49" s="375" t="n">
-        <v>47439.95465122465</v>
+        <v>47439.95465122464</v>
       </c>
       <c r="V49" s="375" t="n">
         <v>56489.12845072968</v>
@@ -11806,7 +11806,7 @@
         <v>541.1087346025606</v>
       </c>
       <c r="Z49" s="372" t="n">
-        <v>586.4221588579423</v>
+        <v>586.4221588579422</v>
       </c>
       <c r="AA49" s="372" t="n">
         <v>676.6004797784625</v>
@@ -11838,13 +11838,13 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>42931.54498093021</v>
+        <v>42931.5449809302</v>
       </c>
       <c r="AL49" s="375" t="n">
         <v>47822.74547710991</v>
       </c>
       <c r="AM49" s="375" t="n">
-        <v>56798.52572575564</v>
+        <v>56798.52572575563</v>
       </c>
       <c r="AN49" s="375" t="n">
         <v>68510.70480999134</v>
@@ -11853,7 +11853,7 @@
         <v>76870.38841578214</v>
       </c>
       <c r="AP49" s="381" t="n">
-        <v>562.0113477819581</v>
+        <v>562.011347781958</v>
       </c>
       <c r="AQ49" s="372" t="n">
         <v>603.8477880951552</v>
@@ -11868,13 +11868,13 @@
         <v>916.5517028147588</v>
       </c>
       <c r="AU49" s="372" t="n">
-        <v>461.9521232689465</v>
+        <v>461.9521232689464</v>
       </c>
       <c r="AV49" s="372" t="n">
         <v>443.6130054491656</v>
       </c>
       <c r="AW49" s="372" t="n">
-        <v>450.4672702865209</v>
+        <v>450.4672702865208</v>
       </c>
       <c r="AX49" s="372" t="n">
         <v>499.6572557510981</v>
@@ -11891,7 +11891,7 @@
         <v>44275.89431326298</v>
       </c>
       <c r="BC49" s="375" t="n">
-        <v>50796.95927066051</v>
+        <v>50796.95927066052</v>
       </c>
       <c r="BD49" s="375" t="n">
         <v>62289.28854629438</v>
@@ -11900,7 +11900,7 @@
         <v>77252.96485072571</v>
       </c>
       <c r="BF49" s="392" t="n">
-        <v>88872.18069931728</v>
+        <v>88872.18069931729</v>
       </c>
       <c r="BG49" s="386" t="n">
         <v>579.6100524288494</v>
@@ -11930,7 +11930,7 @@
         <v>563.4156665444257</v>
       </c>
       <c r="BP49" s="387" t="n">
-        <v>583.9832171489148</v>
+        <v>583.9832171489149</v>
       </c>
       <c r="BR49" s="111" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>77876.15922685125</v>
       </c>
       <c r="BW49" s="392" t="n">
-        <v>89797.18623305204</v>
+        <v>89797.18623305205</v>
       </c>
       <c r="BX49" s="386" t="n">
         <v>579.82830575</v>
@@ -11980,7 +11980,7 @@
         <v>568.2731845328248</v>
       </c>
       <c r="CG49" s="387" t="n">
-        <v>590.3522304168397</v>
+        <v>590.3522304168398</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" thickBot="1">
@@ -12190,16 +12190,16 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>755.2092654082581</v>
+        <v>755.209265408258</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="BW50" s="421" t="n">
         <v>1140.017687397478</v>
@@ -12208,31 +12208,31 @@
         <v>251.8246595737656</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="BZ50" s="417" t="n">
-        <v>413.7600915489919</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="CA50" s="417" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="CB50" s="418" t="n">
-        <v>478.5997687531333</v>
+        <v>478.5997687531332</v>
       </c>
       <c r="CC50" s="417" t="n">
         <v>251.8246595737656</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>379.7415776342887</v>
+        <v>379.7415776342885</v>
       </c>
       <c r="CE50" s="417" t="n">
-        <v>413.7600915489919</v>
+        <v>413.7600915489917</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>445.4766989390283</v>
+        <v>445.4766989390282</v>
       </c>
       <c r="CG50" s="418" t="n">
-        <v>478.5997687531333</v>
+        <v>478.5997687531331</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickBot="1">
@@ -12245,7 +12245,7 @@
         <v>90032.48838082486</v>
       </c>
       <c r="D51" s="425" t="n">
-        <v>92359.96532172996</v>
+        <v>92359.96532172995</v>
       </c>
       <c r="E51" s="425" t="n">
         <v>104753.3644567715</v>
@@ -12260,7 +12260,7 @@
         <v>283.0721252582356</v>
       </c>
       <c r="I51" s="427" t="n">
-        <v>302.8565327461748</v>
+        <v>302.8565327461747</v>
       </c>
       <c r="J51" s="427" t="n">
         <v>341.9611404536604</v>
@@ -12275,7 +12275,7 @@
         <v>240.4338837614253</v>
       </c>
       <c r="N51" s="427" t="n">
-        <v>212.5547961320388</v>
+        <v>212.5547961320387</v>
       </c>
       <c r="O51" s="427" t="n">
         <v>204.1397368201066</v>
@@ -12295,7 +12295,7 @@
         <v>90032.48838082486</v>
       </c>
       <c r="U51" s="430" t="n">
-        <v>92359.96532172996</v>
+        <v>92359.96532172995</v>
       </c>
       <c r="V51" s="430" t="n">
         <v>104753.3644567715</v>
@@ -12310,7 +12310,7 @@
         <v>283.0721252582356</v>
       </c>
       <c r="Z51" s="433" t="n">
-        <v>302.8565327461748</v>
+        <v>302.8565327461747</v>
       </c>
       <c r="AA51" s="433" t="n">
         <v>341.9611404536604</v>
@@ -12322,10 +12322,10 @@
         <v>428.6840076472211</v>
       </c>
       <c r="AD51" s="433" t="n">
-        <v>240.4338837614254</v>
+        <v>240.4338837614253</v>
       </c>
       <c r="AE51" s="433" t="n">
-        <v>212.5547961320388</v>
+        <v>212.5547961320387</v>
       </c>
       <c r="AF51" s="433" t="n">
         <v>204.1397368201066</v>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="AK51" s="435" t="n">
-        <v>90945.65390440408</v>
+        <v>90945.65390440407</v>
       </c>
       <c r="AL51" s="408" t="n">
-        <v>92742.75614761525</v>
+        <v>92742.75614761523</v>
       </c>
       <c r="AM51" s="408" t="n">
-        <v>105062.7617317975</v>
+        <v>105062.7617317974</v>
       </c>
       <c r="AN51" s="408" t="n">
         <v>118615.6026291499</v>
@@ -12363,7 +12363,7 @@
         <v>308.9618231399147</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>348.4691806740313</v>
+        <v>348.4691806740312</v>
       </c>
       <c r="AS51" s="437" t="n">
         <v>398.7714661370073</v>
@@ -12375,7 +12375,7 @@
         <v>243.6946409636917</v>
       </c>
       <c r="AV51" s="437" t="n">
-        <v>214.2743425581509</v>
+        <v>214.2743425581508</v>
       </c>
       <c r="AW51" s="437" t="n">
         <v>205.4312663188236</v>
@@ -12384,7 +12384,7 @@
         <v>218.1963483251425</v>
       </c>
       <c r="AY51" s="438" t="n">
-        <v>224.6798581741623</v>
+        <v>224.6798581741622</v>
       </c>
       <c r="BA51" s="155" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>93981.06660167991</v>
       </c>
       <c r="BC51" s="440" t="n">
-        <v>98851.75761091994</v>
+        <v>98851.75761091997</v>
       </c>
       <c r="BD51" s="440" t="n">
         <v>115508.9825858523</v>
@@ -12410,10 +12410,10 @@
         <v>299.5562674783223</v>
       </c>
       <c r="BH51" s="443" t="n">
-        <v>329.313258745978</v>
+        <v>329.3132587459781</v>
       </c>
       <c r="BI51" s="443" t="n">
-        <v>383.1169089666216</v>
+        <v>383.1169089666215</v>
       </c>
       <c r="BJ51" s="443" t="n">
         <v>450.3829185954293</v>
@@ -12425,7 +12425,7 @@
         <v>251.8282215767555</v>
       </c>
       <c r="BM51" s="443" t="n">
-        <v>228.388676945118</v>
+        <v>228.3886769451181</v>
       </c>
       <c r="BN51" s="443" t="n">
         <v>225.856965614382</v>
@@ -12460,7 +12460,7 @@
         <v>299.321183633328</v>
       </c>
       <c r="BY51" s="417" t="n">
-        <v>329.0122251179391</v>
+        <v>329.012225117939</v>
       </c>
       <c r="BZ51" s="417" t="n">
         <v>382.802596966913</v>
@@ -13653,13 +13653,13 @@
         <v>4473</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>0.6325076527118622</v>
+        <v>0.632507652711862</v>
       </c>
       <c r="CX58" s="92" t="n">
         <v>0.5588274414371716</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5575524490069851</v>
+        <v>0.5575524490069852</v>
       </c>
       <c r="CZ58" s="92" t="n">
         <v>0.5519744899537801</v>
@@ -13668,13 +13668,13 @@
         <v>0.539746239387339</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.003727999122884204</v>
+        <v>0.003727999122884203</v>
       </c>
       <c r="DD58" s="394" t="n">
         <v>0.003650943496526008</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.003733252162249804</v>
+        <v>0.003733252162249805</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.00386861594666747</v>
@@ -14535,7 +14535,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="CB61" s="213" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="CC61" s="212" t="n">
         <v>2.998948818938198</v>
@@ -14550,7 +14550,7 @@
         <v>2.334638820239654</v>
       </c>
       <c r="CG61" s="213" t="n">
-        <v>2.381985453874114</v>
+        <v>2.381985453874115</v>
       </c>
       <c r="CI61" s="211" t="n">
         <v>0</v>
@@ -14580,19 +14580,19 @@
         <v>360</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802453</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945179</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885682</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="AK62" s="220" t="n">
-        <v>59.46086383000001</v>
+        <v>59.46086383</v>
       </c>
       <c r="AL62" s="209" t="n">
         <v>132.64704174</v>
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="BB62" s="221" t="n">
-        <v>59.46086383000001</v>
+        <v>59.46086383</v>
       </c>
       <c r="BC62" s="222" t="n">
         <v>132.64704174</v>
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="BS62" s="221" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="BT62" s="222" t="n">
         <v>131.35525567278</v>
@@ -14835,7 +14835,7 @@
         <v>313.660972772553</v>
       </c>
       <c r="BY62" s="222" t="n">
-        <v>300.7453812153509</v>
+        <v>300.745381215351</v>
       </c>
       <c r="BZ62" s="222" t="n">
         <v>302.8121014439594</v>
@@ -14889,19 +14889,19 @@
         <v>17534</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>0.8136761271070084</v>
+        <v>0.8136761271070082</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7218608518690572</v>
+        <v>0.7218608518690569</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7224227467606011</v>
+        <v>0.722422746760601</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.7193951259160208</v>
+        <v>0.7193951259160206</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.6959031002607986</v>
+        <v>0.6959031002607984</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="BS67" s="236" t="n">
-        <v>71.47924935026253</v>
+        <v>71.47924935026255</v>
       </c>
       <c r="BT67" s="237" t="n">
         <v>56.33223463137914</v>
@@ -15763,10 +15763,10 @@
         <v>55.6562685015753</v>
       </c>
       <c r="BV67" s="237" t="n">
-        <v>51.23859989215607</v>
+        <v>51.23859989215605</v>
       </c>
       <c r="BW67" s="238" t="n">
-        <v>45.51792185462427</v>
+        <v>45.51792185462426</v>
       </c>
       <c r="BX67" s="462" t="n">
         <v>0.4657540040095084</v>
@@ -15778,7 +15778,7 @@
         <v>0.4084440291566179</v>
       </c>
       <c r="CA67" s="463" t="n">
-        <v>0.3918221549312478</v>
+        <v>0.3918221549312477</v>
       </c>
       <c r="CB67" s="464" t="n">
         <v>0.3682217376588177</v>
@@ -15793,10 +15793,10 @@
         <v>55.48203028735139</v>
       </c>
       <c r="CF67" s="200" t="n">
-        <v>51.16885634235307</v>
+        <v>51.16885634235305</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>45.53730210708331</v>
+        <v>45.5373021070833</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="BS68" s="236" t="n">
-        <v>20.23385150235895</v>
+        <v>20.23385150235896</v>
       </c>
       <c r="BT68" s="237" t="n">
         <v>16.0958098959233</v>
@@ -16038,7 +16038,7 @@
         <v>0.2013055629216982</v>
       </c>
       <c r="BZ68" s="463" t="n">
-        <v>0.2116220377663219</v>
+        <v>0.2116220377663218</v>
       </c>
       <c r="CA68" s="463" t="n">
         <v>0.2217157632371279</v>
@@ -16047,13 +16047,13 @@
         <v>0.2241174067434663</v>
       </c>
       <c r="CC68" s="197" t="n">
-        <v>20.18889260083835</v>
+        <v>20.18889260083836</v>
       </c>
       <c r="CD68" s="190" t="n">
         <v>16.09329489865554</v>
       </c>
       <c r="CE68" s="190" t="n">
-        <v>17.45621489358322</v>
+        <v>17.45621489358321</v>
       </c>
       <c r="CF68" s="190" t="n">
         <v>19.03493524529341</v>
@@ -16283,7 +16283,7 @@
         <v>45.33733851771335</v>
       </c>
       <c r="BT69" s="237" t="n">
-        <v>46.47854001102072</v>
+        <v>46.47854001102073</v>
       </c>
       <c r="BU69" s="237" t="n">
         <v>50.45142226201708</v>
@@ -16292,13 +16292,13 @@
         <v>55.51399834326029</v>
       </c>
       <c r="BW69" s="238" t="n">
-        <v>55.46093120356361</v>
+        <v>55.4609312035636</v>
       </c>
       <c r="BX69" s="462" t="n">
         <v>0.5931011032526519</v>
       </c>
       <c r="BY69" s="463" t="n">
-        <v>0.5864807637667118</v>
+        <v>0.5864807637667119</v>
       </c>
       <c r="BZ69" s="463" t="n">
         <v>0.6166436496495232</v>
@@ -16307,13 +16307,13 @@
         <v>0.6932064424993806</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.6609797710301051</v>
+        <v>0.660979771030105</v>
       </c>
       <c r="CC69" s="197" t="n">
         <v>45.37159027563463</v>
       </c>
       <c r="CD69" s="190" t="n">
-        <v>46.5925692761086</v>
+        <v>46.59256927610861</v>
       </c>
       <c r="CE69" s="190" t="n">
         <v>50.68726554576617</v>
@@ -16642,7 +16642,7 @@
         <v>306.259651823</v>
       </c>
       <c r="O71" s="215" t="n">
-        <v>308.3745962560001</v>
+        <v>308.374596256</v>
       </c>
       <c r="P71" s="215" t="n">
         <v>305.04373089</v>
@@ -16692,7 +16692,7 @@
         <v>306.259651823</v>
       </c>
       <c r="AF71" s="218" t="n">
-        <v>308.3745962560001</v>
+        <v>308.374596256</v>
       </c>
       <c r="AG71" s="218" t="n">
         <v>305.04373089</v>
@@ -16721,7 +16721,7 @@
         <v>0.018</v>
       </c>
       <c r="AP71" s="206" t="n">
-        <v>0.74037989966</v>
+        <v>0.7403798996599998</v>
       </c>
       <c r="AQ71" s="207" t="n">
         <v>1.29178606722</v>
@@ -16733,7 +16733,7 @@
         <v>2.70638639645</v>
       </c>
       <c r="AT71" s="208" t="n">
-        <v>3.42680300226</v>
+        <v>3.426803002260001</v>
       </c>
       <c r="AU71" s="207" t="n">
         <v>314.47464889966</v>
@@ -16771,7 +16771,7 @@
         <v>0.018</v>
       </c>
       <c r="BG71" s="221" t="n">
-        <v>0.74037989966</v>
+        <v>0.7403798996599998</v>
       </c>
       <c r="BH71" s="222" t="n">
         <v>1.29178606722</v>
@@ -16783,7 +16783,7 @@
         <v>2.70638639645</v>
       </c>
       <c r="BK71" s="214" t="n">
-        <v>3.42680300226</v>
+        <v>3.426803002260001</v>
       </c>
       <c r="BL71" s="222" t="n">
         <v>314.47464889966</v>
@@ -16815,7 +16815,7 @@
         <v>125.8143879751312</v>
       </c>
       <c r="BV71" s="272" t="n">
-        <v>128.0366376123743</v>
+        <v>128.0366376123742</v>
       </c>
       <c r="BW71" s="273" t="n">
         <v>123.1276364700726</v>
@@ -16824,13 +16824,13 @@
         <v>0.4422912017091774</v>
       </c>
       <c r="BY71" s="467" t="n">
-        <v>0.4020516272219036</v>
+        <v>0.4020516272219035</v>
       </c>
       <c r="BZ71" s="467" t="n">
         <v>0.4158147707356966</v>
       </c>
       <c r="CA71" s="467" t="n">
-        <v>0.4289762806318075</v>
+        <v>0.4289762806318074</v>
       </c>
       <c r="CB71" s="468" t="n">
         <v>0.413283389747968</v>
@@ -18572,7 +18572,7 @@
         <v>0.4755947700452125</v>
       </c>
       <c r="M80" s="495" t="n">
-        <v>0.1486428264486221</v>
+        <v>0.148642826448622</v>
       </c>
       <c r="N80" s="495" t="n">
         <v>0.2951820885819316</v>
@@ -18581,7 +18581,7 @@
         <v>0.399050242938167</v>
       </c>
       <c r="P80" s="495" t="n">
-        <v>0.4406575824926322</v>
+        <v>0.4406575824926321</v>
       </c>
       <c r="Q80" s="496" t="n">
         <v>0.4696196943955239</v>
@@ -18622,7 +18622,7 @@
         <v>0.4755947700452125</v>
       </c>
       <c r="AD80" s="498" t="n">
-        <v>0.1486428264486221</v>
+        <v>0.148642826448622</v>
       </c>
       <c r="AE80" s="498" t="n">
         <v>0.2951820885819316</v>
@@ -18631,7 +18631,7 @@
         <v>0.399050242938167</v>
       </c>
       <c r="AG80" s="498" t="n">
-        <v>0.4406575824926322</v>
+        <v>0.4406575824926321</v>
       </c>
       <c r="AH80" s="499" t="n">
         <v>0.4696196943955239</v>
@@ -18642,7 +18642,7 @@
         </is>
       </c>
       <c r="AK80" s="206" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="AL80" s="207" t="n">
         <v>131.35525567278</v>
@@ -18657,13 +18657,13 @@
         <v>273.22388770774</v>
       </c>
       <c r="AP80" s="500" t="n">
-        <v>0.1593291514256859</v>
+        <v>0.1593291514256858</v>
       </c>
       <c r="AQ80" s="501" t="n">
         <v>0.3064698402523479</v>
       </c>
       <c r="AR80" s="501" t="n">
-        <v>0.4104750786813761</v>
+        <v>0.410475078681376</v>
       </c>
       <c r="AS80" s="501" t="n">
         <v>0.4528285826494517</v>
@@ -18678,7 +18678,7 @@
         <v>0.3034852771255115</v>
       </c>
       <c r="AW80" s="501" t="n">
-        <v>0.4064930271378045</v>
+        <v>0.4064930271378044</v>
       </c>
       <c r="AX80" s="501" t="n">
         <v>0.447850117626528</v>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="BB80" s="221" t="n">
-        <v>58.72048393034001</v>
+        <v>58.72048393034</v>
       </c>
       <c r="BC80" s="222" t="n">
         <v>131.35525567278</v>
@@ -18707,13 +18707,13 @@
         <v>273.22388770774</v>
       </c>
       <c r="BG80" s="503" t="n">
-        <v>0.1593291514256859</v>
+        <v>0.1593291514256858</v>
       </c>
       <c r="BH80" s="504" t="n">
         <v>0.3064698402523479</v>
       </c>
       <c r="BI80" s="504" t="n">
-        <v>0.4104750786813761</v>
+        <v>0.410475078681376</v>
       </c>
       <c r="BJ80" s="504" t="n">
         <v>0.4528285826494517</v>
@@ -18728,7 +18728,7 @@
         <v>0.3034852771255115</v>
       </c>
       <c r="BN80" s="504" t="n">
-        <v>0.4064930271378045</v>
+        <v>0.4064930271378044</v>
       </c>
       <c r="BO80" s="504" t="n">
         <v>0.447850117626528</v>
@@ -20284,7 +20284,7 @@
         <v>79935.96700635315</v>
       </c>
       <c r="BT91" s="440" t="n">
-        <v>172764.2669604354</v>
+        <v>172764.2669604353</v>
       </c>
       <c r="BU91" s="440" t="n">
         <v>262918.0900022708</v>
@@ -20987,10 +20987,10 @@
         <v>980.9518563653344</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>62744.73673092617</v>
+        <v>62744.73673092618</v>
       </c>
       <c r="AV96" s="375" t="n">
-        <v>57819.84417732574</v>
+        <v>57819.84417732573</v>
       </c>
       <c r="AW96" s="375" t="n">
         <v>60662.44851795745</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>51470.907238572</v>
+        <v>51470.90723857199</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>45635.36296202838</v>
+        <v>45635.36296202836</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>48298.66965794648</v>
+        <v>48298.66965794646</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>48006.25177536016</v>
+        <v>48006.25177536013</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47632.48598332283</v>
+        <v>47632.48598332282</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21214,7 +21214,7 @@
         <v>2679.065581588176</v>
       </c>
       <c r="AU97" s="379" t="n">
-        <v>45456.50369077885</v>
+        <v>45456.50369077884</v>
       </c>
       <c r="AV97" s="375" t="n">
         <v>43702.50065591514</v>
@@ -21323,10 +21323,10 @@
         <v>41785.52761429289</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>47557.42876343117</v>
+        <v>47557.42876343116</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>52673.28590197934</v>
+        <v>52673.28590197933</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21444,7 +21444,7 @@
         <v>91957.61105517835</v>
       </c>
       <c r="AV98" s="375" t="n">
-        <v>109522.0380868604</v>
+        <v>109522.0380868603</v>
       </c>
       <c r="AW98" s="375" t="n">
         <v>126384.8968960265</v>
@@ -21541,10 +21541,10 @@
         <v>0</v>
       </c>
       <c r="DC98" s="391" t="n">
-        <v>86939.04257686155</v>
+        <v>86939.04257686157</v>
       </c>
       <c r="DD98" s="375" t="n">
-        <v>98048.50521146077</v>
+        <v>98048.50521146078</v>
       </c>
       <c r="DE98" s="375" t="n">
         <v>117808.7224934889</v>
@@ -21726,7 +21726,7 @@
         <v>56336.58065301581</v>
       </c>
       <c r="BT99" s="420" t="n">
-        <v>5785.615095177032</v>
+        <v>5785.615095177034</v>
       </c>
       <c r="BU99" s="420" t="n">
         <v>6259.511928912306</v>
@@ -21735,7 +21735,7 @@
         <v>6705.77757134998</v>
       </c>
       <c r="BW99" s="421" t="n">
-        <v>7183.859279408347</v>
+        <v>7183.859279408349</v>
       </c>
       <c r="BX99" s="416" t="n">
         <v>18785.44251814282</v>
@@ -21771,16 +21771,16 @@
         <v>4417.155833572388</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>4764.761531358742</v>
+        <v>4764.761531358741</v>
       </c>
       <c r="DE99" s="420" t="n">
         <v>5167.082612807762</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>5549.162947051829</v>
+        <v>5549.162947051828</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>5955.299443910369</v>
+        <v>5955.299443910368</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21822,7 +21822,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="L100" s="428" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="S100" s="143" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="AC100" s="434" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="AJ100" s="150" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>514533.445461</v>
       </c>
       <c r="AN100" s="408" t="n">
-        <v>560230.2540480001</v>
+        <v>560230.254048</v>
       </c>
       <c r="AO100" s="409" t="n">
         <v>611485.4023739999</v>
@@ -21924,7 +21924,7 @@
         <v>514533.445461</v>
       </c>
       <c r="BE100" s="440" t="n">
-        <v>560230.2540480001</v>
+        <v>560230.254048</v>
       </c>
       <c r="BF100" s="441" t="n">
         <v>611485.4023739999</v>
@@ -21997,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>183894.2944741637</v>
+        <v>183894.2944741638</v>
       </c>
       <c r="DD100" s="440" t="n">
         <v>185270.0027578279</v>
@@ -22006,7 +22006,7 @@
         <v>213060.002378536</v>
       </c>
       <c r="DF100" s="440" t="n">
-        <v>244491.9258505616</v>
+        <v>244491.9258505615</v>
       </c>
       <c r="DG100" s="441" t="n">
         <v>273672.1247265292</v>
@@ -23138,13 +23138,13 @@
         <v>2844</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>0.6325076527118622</v>
+        <v>0.632507652711862</v>
       </c>
       <c r="CX108" s="200" t="n">
         <v>0.5588274414371716</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5575524490069851</v>
+        <v>0.5575524490069852</v>
       </c>
       <c r="CZ108" s="200" t="n">
         <v>0.5519744899537801</v>
@@ -24023,19 +24023,19 @@
         <v>2178</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802453</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945179</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885682</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24061,7 +24061,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H112" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I112" s="215" t="n">
         <v>258.2717129066096</v>
@@ -24070,7 +24070,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="K112" s="215" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="L112" s="216" t="n">
         <v>182.5988128429346</v>
@@ -24082,7 +24082,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="O112" s="215" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="P112" s="215" t="n">
         <v>199.9191344202025</v>
@@ -24111,7 +24111,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y112" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z112" s="218" t="n">
         <v>258.2717129066096</v>
@@ -24120,7 +24120,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="AB112" s="218" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="AC112" s="219" t="n">
         <v>182.5988128429346</v>
@@ -24132,7 +24132,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="AF112" s="218" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="AG112" s="218" t="n">
         <v>199.9191344202025</v>
@@ -24164,7 +24164,7 @@
         <v>301.0218825085427</v>
       </c>
       <c r="AQ112" s="207" t="n">
-        <v>259.972299350457</v>
+        <v>259.9722993504571</v>
       </c>
       <c r="AR112" s="207" t="n">
         <v>195.9572318509365</v>
@@ -24214,7 +24214,7 @@
         <v>301.0218825085427</v>
       </c>
       <c r="BH112" s="222" t="n">
-        <v>259.972299350457</v>
+        <v>259.9722993504571</v>
       </c>
       <c r="BI112" s="222" t="n">
         <v>195.9572318509365</v>
@@ -24318,19 +24318,19 @@
         <v>22276</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>0.8136761271070084</v>
+        <v>0.8136761271070082</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7218608518690572</v>
+        <v>0.7218608518690569</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7224227467606011</v>
+        <v>0.722422746760601</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.7193951259160208</v>
+        <v>0.7193951259160206</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.6959031002607986</v>
+        <v>0.6959031002607984</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -25716,7 +25716,7 @@
         <v>0.1481374028113281</v>
       </c>
       <c r="CC119" s="197" t="n">
-        <v>14.27934975127428</v>
+        <v>14.27934975127427</v>
       </c>
       <c r="CD119" s="190" t="n">
         <v>5.41840906430786</v>
@@ -26217,7 +26217,7 @@
         <v>0.05766731015337993</v>
       </c>
       <c r="CB121" s="468" t="n">
-        <v>0.08106838078708535</v>
+        <v>0.08106838078708534</v>
       </c>
       <c r="CC121" s="212" t="n">
         <v>24.3735728873113</v>
@@ -27911,28 +27911,28 @@
         <v>0.01784808841815988</v>
       </c>
       <c r="I130" s="495" t="n">
-        <v>0.02644403715310645</v>
+        <v>0.02644403715310646</v>
       </c>
       <c r="J130" s="495" t="n">
-        <v>0.06540160586902488</v>
+        <v>0.0654016058690249</v>
       </c>
       <c r="K130" s="495" t="n">
-        <v>0.0856136222994042</v>
+        <v>0.08561362229940421</v>
       </c>
       <c r="L130" s="496" t="n">
         <v>0.08911974768298138</v>
       </c>
       <c r="M130" s="495" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="N130" s="495" t="n">
         <v>0.02604799752893461</v>
       </c>
       <c r="O130" s="495" t="n">
-        <v>0.06470606122154865</v>
+        <v>0.06470606122154866</v>
       </c>
       <c r="P130" s="495" t="n">
-        <v>0.08468563942390696</v>
+        <v>0.08468563942390697</v>
       </c>
       <c r="Q130" s="496" t="n">
         <v>0.08797725656616802</v>
@@ -27961,28 +27961,28 @@
         <v>0.01784808841815988</v>
       </c>
       <c r="Z130" s="498" t="n">
-        <v>0.02644403715310645</v>
+        <v>0.02644403715310646</v>
       </c>
       <c r="AA130" s="498" t="n">
-        <v>0.06540160586902488</v>
+        <v>0.0654016058690249</v>
       </c>
       <c r="AB130" s="498" t="n">
-        <v>0.0856136222994042</v>
+        <v>0.08561362229940421</v>
       </c>
       <c r="AC130" s="499" t="n">
         <v>0.08911974768298138</v>
       </c>
       <c r="AD130" s="498" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="AE130" s="498" t="n">
         <v>0.02604799752893461</v>
       </c>
       <c r="AF130" s="498" t="n">
-        <v>0.06470606122154865</v>
+        <v>0.06470606122154866</v>
       </c>
       <c r="AG130" s="498" t="n">
-        <v>0.08468563942390696</v>
+        <v>0.08468563942390697</v>
       </c>
       <c r="AH130" s="499" t="n">
         <v>0.08797725656616802</v>
@@ -28017,7 +28017,7 @@
         <v>0.06486477924766289</v>
       </c>
       <c r="AS130" s="501" t="n">
-        <v>0.08487377617971928</v>
+        <v>0.08487377617971927</v>
       </c>
       <c r="AT130" s="502" t="n">
         <v>0.08844011763846212</v>
@@ -28032,7 +28032,7 @@
         <v>0.06417494373955945</v>
       </c>
       <c r="AX130" s="501" t="n">
-        <v>0.08395381264169581</v>
+        <v>0.0839538126416958</v>
       </c>
       <c r="AY130" s="502" t="n">
         <v>0.08730633919542499</v>
@@ -28067,7 +28067,7 @@
         <v>0.06486477924766289</v>
       </c>
       <c r="BJ130" s="504" t="n">
-        <v>0.08487377617971928</v>
+        <v>0.08487377617971927</v>
       </c>
       <c r="BK130" s="505" t="n">
         <v>0.08844011763846212</v>
@@ -28082,7 +28082,7 @@
         <v>0.06417494373955945</v>
       </c>
       <c r="BO130" s="504" t="n">
-        <v>0.08395381264169581</v>
+        <v>0.0839538126416958</v>
       </c>
       <c r="BP130" s="505" t="n">
         <v>0.08730633919542499</v>
@@ -30326,13 +30326,13 @@
         <v>489.9393772395445</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>471.5664447721919</v>
+        <v>471.5664447721917</v>
       </c>
       <c r="CX146" s="512" t="n">
         <v>447.1539032149584</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>475.8887582186935</v>
+        <v>475.8887582186936</v>
       </c>
       <c r="CZ146" s="512" t="n">
         <v>501.0331779117008</v>
@@ -30518,7 +30518,7 @@
         <v>1543.329831969467</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>209.089063316188</v>
+        <v>209.0890633161881</v>
       </c>
       <c r="CX147" s="375" t="n">
         <v>182.3742324386158</v>
@@ -30902,19 +30902,19 @@
         <v>26563.90922549893</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>117.1118499841886</v>
+        <v>117.1118499841845</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>16.66360582296741</v>
+        <v>16.66360582296683</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>18.02852008769406</v>
+        <v>18.02852008769344</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>19.31384565002039</v>
+        <v>19.31384565001972</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>20.69080559165297</v>
+        <v>20.69080559165225</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -30927,7 +30927,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="D150" s="425" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="E150" s="425" t="n">
         <v>719731.1510085932</v>
@@ -30936,19 +30936,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="G150" s="426" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="H150" s="427" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="I150" s="427" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="J150" s="427" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="K150" s="427" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="L150" s="428" t="n">
         <v>3893.954745988455</v>
@@ -30962,7 +30962,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="U150" s="430" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="V150" s="430" t="n">
         <v>719731.1510085932</v>
@@ -30971,19 +30971,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="X150" s="431" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="Y150" s="432" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="Z150" s="433" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="AA150" s="433" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="AB150" s="433" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="AC150" s="434" t="n">
         <v>3893.954745988455</v>
@@ -30997,31 +30997,31 @@
         <v>917464.158603146</v>
       </c>
       <c r="AL150" s="408" t="n">
-        <v>881119.0390104104</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="AM150" s="408" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="AN150" s="408" t="n">
         <v>680667.3787439771</v>
       </c>
       <c r="AO150" s="409" t="n">
-        <v>713881.7621042943</v>
+        <v>713881.7621042944</v>
       </c>
       <c r="AP150" s="436" t="n">
         <v>3047.832107611343</v>
       </c>
       <c r="AQ150" s="437" t="n">
-        <v>3389.280478004363</v>
+        <v>3389.280478004362</v>
       </c>
       <c r="AR150" s="437" t="n">
-        <v>3693.085197699454</v>
+        <v>3693.085197699453</v>
       </c>
       <c r="AS150" s="437" t="n">
         <v>3688.333869463637</v>
       </c>
       <c r="AT150" s="438" t="n">
-        <v>3876.857014318611</v>
+        <v>3876.857014318612</v>
       </c>
       <c r="BA150" s="155" t="inlineStr">
         <is>
@@ -31032,31 +31032,31 @@
         <v>917464.158603146</v>
       </c>
       <c r="BC150" s="440" t="n">
-        <v>881119.0390104104</v>
+        <v>881119.0390104103</v>
       </c>
       <c r="BD150" s="440" t="n">
-        <v>723686.7523308534</v>
+        <v>723686.7523308533</v>
       </c>
       <c r="BE150" s="440" t="n">
         <v>680667.3787439771</v>
       </c>
       <c r="BF150" s="441" t="n">
-        <v>713881.7621042943</v>
+        <v>713881.7621042944</v>
       </c>
       <c r="BG150" s="442" t="n">
         <v>3047.832107611343</v>
       </c>
       <c r="BH150" s="443" t="n">
-        <v>3389.280478004363</v>
+        <v>3389.280478004362</v>
       </c>
       <c r="BI150" s="443" t="n">
-        <v>3693.085197699454</v>
+        <v>3693.085197699453</v>
       </c>
       <c r="BJ150" s="443" t="n">
         <v>3688.333869463637</v>
       </c>
       <c r="BK150" s="444" t="n">
-        <v>3876.857014318611</v>
+        <v>3876.857014318612</v>
       </c>
       <c r="BR150" s="155" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         </is>
       </c>
       <c r="BS150" s="439" t="n">
-        <v>919949.0472291016</v>
+        <v>919949.0472291018</v>
       </c>
       <c r="BT150" s="440" t="n">
         <v>884374.6133376467</v>
@@ -31079,7 +31079,7 @@
         <v>720938.7674062786</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>3047.176408873211</v>
+        <v>3047.176408873212</v>
       </c>
       <c r="BY150" s="443" t="n">
         <v>3391.017038204623</v>
@@ -31094,19 +31094,19 @@
         <v>3895.613624696012</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>954.9076852500773</v>
+        <v>954.9076852500731</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>812.9159754760085</v>
+        <v>812.9159754760079</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>873.3667611711487</v>
+        <v>873.3667611711483</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>943.4993577474819</v>
+        <v>943.4993577474813</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>971.3116997644757</v>
+        <v>971.3116997644751</v>
       </c>
     </row>
     <row r="151">
@@ -35232,7 +35232,7 @@
         <v>545.361341</v>
       </c>
       <c r="Q176" s="216" t="n">
-        <v>575.0631740000001</v>
+        <v>575.063174</v>
       </c>
       <c r="S176" s="143" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>545.361341</v>
       </c>
       <c r="AH176" s="219" t="n">
-        <v>575.0631740000001</v>
+        <v>575.063174</v>
       </c>
       <c r="AJ176" s="150" t="inlineStr">
         <is>
@@ -35376,13 +35376,13 @@
         <v>432.822496915</v>
       </c>
       <c r="BN176" s="222" t="n">
-        <v>511.4253719110001</v>
+        <v>511.425371911</v>
       </c>
       <c r="BO176" s="222" t="n">
-        <v>543.618642707</v>
+        <v>543.6186427069999</v>
       </c>
       <c r="BP176" s="214" t="n">
-        <v>573.52267978</v>
+        <v>573.5226797800001</v>
       </c>
       <c r="BR176" s="155" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>302.812101667542</v>
       </c>
       <c r="CA176" s="222" t="n">
-        <v>299.4395746827609</v>
+        <v>299.4395746827608</v>
       </c>
       <c r="CB176" s="214" t="n">
         <v>299.6028889730839</v>
@@ -35429,7 +35429,7 @@
         <v>510.702949163542</v>
       </c>
       <c r="CF176" s="222" t="n">
-        <v>542.8992475817608</v>
+        <v>542.899247581761</v>
       </c>
       <c r="CG176" s="214" t="n">
         <v>572.8267766790839</v>
@@ -38470,10 +38470,10 @@
         <v>135.4621367577627</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>129.9212678290773</v>
+        <v>129.9212678290772</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>122.7006859698305</v>
+        <v>122.7006859698304</v>
       </c>
       <c r="AU190" s="190" t="n">
         <v>168.5530568455</v>
@@ -38482,10 +38482,10 @@
         <v>193.5721394432553</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>233.2377229516893</v>
+        <v>233.2377229516892</v>
       </c>
       <c r="AX190" s="190" t="n">
-        <v>244.5502230780749</v>
+        <v>244.5502230780748</v>
       </c>
       <c r="AY190" s="196" t="n">
         <v>251.2021686833873</v>
@@ -38520,10 +38520,10 @@
         <v>135.4621367577627</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>129.9212678290773</v>
+        <v>129.9212678290772</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>122.7006859698305</v>
+        <v>122.7006859698304</v>
       </c>
       <c r="BL190" s="199" t="n">
         <v>168.5530568452457</v>
@@ -38535,10 +38535,10 @@
         <v>233.2377229517627</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>244.5502230780773</v>
+        <v>244.5502230780772</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>251.2021686838305</v>
+        <v>251.2021686838304</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38567,13 +38567,13 @@
         <v>139.1356978786665</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>135.8375352005599</v>
+        <v>135.8375352005598</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>130.5920444545108</v>
+        <v>130.5920444545107</v>
       </c>
       <c r="CB190" s="198" t="n">
-        <v>123.6681527425452</v>
+        <v>123.6681527425451</v>
       </c>
       <c r="CC190" s="199" t="n">
         <v>167.922472326115</v>
@@ -38582,13 +38582,13 @@
         <v>193.0133120016665</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>232.6801705025599</v>
+        <v>232.6801705025598</v>
       </c>
       <c r="CF190" s="200" t="n">
-        <v>243.9982485885108</v>
+        <v>243.9982485885107</v>
       </c>
       <c r="CG190" s="201" t="n">
-        <v>250.6624224445452</v>
+        <v>250.6624224445451</v>
       </c>
       <c r="CI190" s="199" t="n">
         <v>0</v>
@@ -38618,13 +38618,13 @@
         <v>4473</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>0.6305845188212781</v>
+        <v>0.630584518821278</v>
       </c>
       <c r="CX190" s="92" t="n">
         <v>0.558827441437645</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5575524490099094</v>
+        <v>0.5575524490099095</v>
       </c>
       <c r="CZ190" s="92" t="n">
         <v>0.5519744899569327</v>
@@ -38639,13 +38639,13 @@
         <v>0.003650943499103834</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.003733252168925712</v>
+        <v>0.003733252168925715</v>
       </c>
       <c r="DF190" s="394" t="n">
-        <v>0.00386861595175697</v>
+        <v>0.003868615951756972</v>
       </c>
       <c r="DG190" s="395" t="n">
-        <v>0.004025408043775219</v>
+        <v>0.004025408043775221</v>
       </c>
     </row>
     <row r="191">
@@ -38770,19 +38770,19 @@
         <v>79.835566996</v>
       </c>
       <c r="AP191" s="194" t="n">
-        <v>81.59394147686068</v>
+        <v>81.59394147686069</v>
       </c>
       <c r="AQ191" s="179" t="n">
         <v>79.63781580564702</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>81.97142012176489</v>
+        <v>81.97142012176492</v>
       </c>
       <c r="AS191" s="179" t="n">
         <v>85.14011399953935</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>87.91333277020928</v>
+        <v>87.91333277020927</v>
       </c>
       <c r="AU191" s="190" t="n">
         <v>108.7018404877673</v>
@@ -38791,7 +38791,7 @@
         <v>129.2203678213852</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>149.80480563611</v>
+        <v>149.8048056361101</v>
       </c>
       <c r="AX191" s="190" t="n">
         <v>159.6116553915466</v>
@@ -38820,19 +38820,19 @@
         <v>79.835566996</v>
       </c>
       <c r="BG191" s="197" t="n">
-        <v>81.59394147686068</v>
+        <v>81.59394147686069</v>
       </c>
       <c r="BH191" s="190" t="n">
         <v>79.63781580564702</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>81.97142012176489</v>
+        <v>81.97142012176492</v>
       </c>
       <c r="BJ191" s="190" t="n">
         <v>85.14011399953935</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>87.91333277020928</v>
+        <v>87.91333277020927</v>
       </c>
       <c r="BL191" s="197" t="n">
         <v>108.7018404878607</v>
@@ -38870,19 +38870,19 @@
         <v>78.82907359699999</v>
       </c>
       <c r="BX191" s="197" t="n">
-        <v>81.7141761874246</v>
+        <v>81.71417618742461</v>
       </c>
       <c r="BY191" s="190" t="n">
         <v>79.94461069946261</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>82.48769884133459</v>
+        <v>82.48769884133462</v>
       </c>
       <c r="CA191" s="190" t="n">
         <v>85.85287291835392</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>88.84548259145755</v>
+        <v>88.84548259145754</v>
       </c>
       <c r="CC191" s="197" t="n">
         <v>108.6046715174246</v>
@@ -38933,7 +38933,7 @@
         <v>0.08086620964934653</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>0.08294050297335381</v>
+        <v>0.0829405029733538</v>
       </c>
       <c r="CZ191" s="103" t="n">
         <v>0.08529935814312077</v>
@@ -38942,19 +38942,19 @@
         <v>0.07434357734897763</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.0008974985628294915</v>
+        <v>0.0008974985628294913</v>
       </c>
       <c r="DD191" s="397" t="n">
         <v>0.0007570093182035955</v>
       </c>
       <c r="DE191" s="397" t="n">
-        <v>0.0007380626295865598</v>
+        <v>0.0007380626295865596</v>
       </c>
       <c r="DF191" s="397" t="n">
         <v>0.0007135143082801443</v>
       </c>
       <c r="DG191" s="398" t="n">
-        <v>0.0005541650334209043</v>
+        <v>0.0005541650334209044</v>
       </c>
     </row>
     <row r="192">
@@ -39079,31 +39079,31 @@
         <v>68.313640998</v>
       </c>
       <c r="AP192" s="194" t="n">
-        <v>76.38910727404419</v>
+        <v>76.38910727404415</v>
       </c>
       <c r="AQ192" s="179" t="n">
-        <v>79.19668896951393</v>
+        <v>79.19668896951387</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>81.76962101062628</v>
+        <v>81.76962101062634</v>
       </c>
       <c r="AS192" s="179" t="n">
-        <v>80.04983821064681</v>
+        <v>80.0498382106469</v>
       </c>
       <c r="AT192" s="195" t="n">
         <v>83.86912411019689</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>92.93505310856996</v>
+        <v>92.93505310856992</v>
       </c>
       <c r="AV192" s="190" t="n">
-        <v>107.8028481453051</v>
+        <v>107.802848145305</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>126.08801898962</v>
+        <v>126.0880189896201</v>
       </c>
       <c r="AX192" s="190" t="n">
-        <v>137.1154008642333</v>
+        <v>137.1154008642334</v>
       </c>
       <c r="AY192" s="196" t="n">
         <v>152.182765108134</v>
@@ -39129,22 +39129,22 @@
         <v>68.313640998</v>
       </c>
       <c r="BG192" s="197" t="n">
-        <v>76.38910727404419</v>
+        <v>76.38910727404415</v>
       </c>
       <c r="BH192" s="190" t="n">
-        <v>79.19668896951393</v>
+        <v>79.19668896951387</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>81.76962101062628</v>
+        <v>81.76962101062634</v>
       </c>
       <c r="BJ192" s="190" t="n">
-        <v>80.04983821064681</v>
+        <v>80.0498382106469</v>
       </c>
       <c r="BK192" s="198" t="n">
         <v>83.86912411019689</v>
       </c>
       <c r="BL192" s="197" t="n">
-        <v>92.93505310904419</v>
+        <v>92.93505310904415</v>
       </c>
       <c r="BM192" s="190" t="n">
         <v>107.8028481455139</v>
@@ -39153,7 +39153,7 @@
         <v>126.0880189896263</v>
       </c>
       <c r="BO192" s="190" t="n">
-        <v>137.1154008646468</v>
+        <v>137.1154008646469</v>
       </c>
       <c r="BP192" s="198" t="n">
         <v>152.1827651081969</v>
@@ -39179,22 +39179,22 @@
         <v>67.400544407</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>76.49958990117634</v>
+        <v>76.49958990117629</v>
       </c>
       <c r="BY192" s="190" t="n">
-        <v>79.44432645825334</v>
+        <v>79.44432645825329</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>82.19863381573988</v>
+        <v>82.19863381573994</v>
       </c>
       <c r="CA192" s="190" t="n">
-        <v>80.66001811691194</v>
+        <v>80.66001811691203</v>
       </c>
       <c r="CB192" s="198" t="n">
         <v>84.70726796344694</v>
       </c>
       <c r="CC192" s="197" t="n">
-        <v>92.85966563017634</v>
+        <v>92.85966563017629</v>
       </c>
       <c r="CD192" s="190" t="n">
         <v>107.7270770902533</v>
@@ -39203,7 +39203,7 @@
         <v>126.0126797187399</v>
       </c>
       <c r="CF192" s="190" t="n">
-        <v>137.0400037669119</v>
+        <v>137.040003766912</v>
       </c>
       <c r="CG192" s="198" t="n">
         <v>152.1078123704469</v>
@@ -39236,7 +39236,7 @@
         <v>4927</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>0.07538747908594198</v>
+        <v>0.07538747908594197</v>
       </c>
       <c r="CX192" s="103" t="n">
         <v>0.07577105569712549</v>
@@ -39245,22 +39245,22 @@
         <v>0.0753392708449033</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>0.07539709805810331</v>
+        <v>0.07539709805810332</v>
       </c>
       <c r="DA192" s="104" t="n">
         <v>0.07495273739913609</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.0008781181330252831</v>
+        <v>0.0008781181330252835</v>
       </c>
       <c r="DD192" s="397" t="n">
-        <v>0.0008389434949003056</v>
+        <v>0.0008389434949003063</v>
       </c>
       <c r="DE192" s="397" t="n">
-        <v>0.0007959552280857857</v>
+        <v>0.0007959552280857852</v>
       </c>
       <c r="DF192" s="397" t="n">
-        <v>0.0007992739312863757</v>
+        <v>0.0007992739312863749</v>
       </c>
       <c r="DG192" s="398" t="n">
         <v>0.0007557095769810143</v>
@@ -39388,34 +39388,34 @@
         <v>0</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="AR193" s="207" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="AW193" s="209" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,34 +39438,34 @@
         <v>0</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="BI193" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="BN193" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,34 +39488,34 @@
         <v>0</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>2.998948607663956</v>
+        <v>2.998948607663959</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>2.220745359731473</v>
+        <v>2.22074535973147</v>
       </c>
       <c r="BZ193" s="212" t="n">
         <v>2.288233811213716</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>2.334639192905131</v>
+        <v>2.334639192905134</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>2.381985675737247</v>
+        <v>2.381985675737244</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>2.998948607663956</v>
+        <v>2.998948607663959</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>2.220745359731473</v>
+        <v>2.22074535973147</v>
       </c>
       <c r="CE193" s="212" t="n">
         <v>2.288233811213716</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>2.334639192905131</v>
+        <v>2.334639192905134</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>2.381985675737247</v>
+        <v>2.381985675737244</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>0</v>
@@ -39545,19 +39545,19 @@
         <v>360</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.006234181061802671</v>
+        <v>0.006234181061802452</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.006396145085788304</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945178</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.006724179760346101</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885683</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39624,7 +39624,7 @@
         <v>545.361341</v>
       </c>
       <c r="Q194" s="216" t="n">
-        <v>575.0631740000001</v>
+        <v>575.063174</v>
       </c>
       <c r="S194" s="143" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>545.361341</v>
       </c>
       <c r="AH194" s="219" t="n">
-        <v>575.0631740000001</v>
+        <v>575.063174</v>
       </c>
       <c r="AJ194" s="150" t="inlineStr">
         <is>
@@ -39697,16 +39697,16 @@
         <v>276.650690708</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>313.7342693978764</v>
+        <v>313.7342693978763</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>300.175455181754</v>
+        <v>300.1754551817539</v>
       </c>
       <c r="AR194" s="207" t="n">
         <v>301.4980022253026</v>
       </c>
       <c r="AS194" s="207" t="n">
-        <v>297.4525834119289</v>
+        <v>297.452583411929</v>
       </c>
       <c r="AT194" s="208" t="n">
         <v>296.8719890720997</v>
@@ -39715,16 +39715,16 @@
         <v>373.195133230563</v>
       </c>
       <c r="AV194" s="207" t="n">
-        <v>432.8224969147628</v>
+        <v>432.8224969147627</v>
       </c>
       <c r="AW194" s="207" t="n">
-        <v>511.425371912568</v>
+        <v>511.4253719125681</v>
       </c>
       <c r="AX194" s="207" t="n">
         <v>543.6186427065202</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>573.5226797797415</v>
+        <v>573.5226797797413</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39747,16 +39747,16 @@
         <v>276.650690708</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>313.7342693978764</v>
+        <v>313.7342693978763</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>300.175455181754</v>
+        <v>300.1754551817539</v>
       </c>
       <c r="BI194" s="222" t="n">
         <v>301.4980022253026</v>
       </c>
       <c r="BJ194" s="222" t="n">
-        <v>297.4525834119289</v>
+        <v>297.452583411929</v>
       </c>
       <c r="BK194" s="214" t="n">
         <v>296.8719890720997</v>
@@ -39765,7 +39765,7 @@
         <v>373.1951332308764</v>
       </c>
       <c r="BM194" s="222" t="n">
-        <v>432.822496914754</v>
+        <v>432.8224969147539</v>
       </c>
       <c r="BN194" s="222" t="n">
         <v>511.4253719123026</v>
@@ -39797,25 +39797,25 @@
         <v>273.223887706</v>
       </c>
       <c r="BX194" s="221" t="n">
-        <v>313.6652741493799</v>
+        <v>313.6652741493798</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>300.7453803961139</v>
+        <v>300.7453803961138</v>
       </c>
       <c r="BZ194" s="222" t="n">
         <v>302.8121016688481</v>
       </c>
       <c r="CA194" s="222" t="n">
-        <v>299.4395746826817</v>
+        <v>299.4395746826818</v>
       </c>
       <c r="CB194" s="214" t="n">
-        <v>299.602888973187</v>
+        <v>299.6028889731869</v>
       </c>
       <c r="CC194" s="222" t="n">
         <v>372.3857580813798</v>
       </c>
       <c r="CD194" s="222" t="n">
-        <v>432.1006360641139</v>
+        <v>432.1006360641138</v>
       </c>
       <c r="CE194" s="222" t="n">
         <v>510.7029491648481</v>
@@ -39854,19 +39854,19 @@
         <v>17534</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>0.8093751493808196</v>
+        <v>0.8093751493808192</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7218608518699053</v>
+        <v>0.721860851869905</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.7224227467631119</v>
+        <v>0.7224227467631118</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.7193951259185029</v>
+        <v>0.7193951259185026</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.6959031002622666</v>
+        <v>0.6959031002622664</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40828,7 +40828,7 @@
         <v>0.5807164183297657</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>0.9329508918067573</v>
+        <v>0.9329508918067571</v>
       </c>
       <c r="AS199" s="190" t="n">
         <v>1.222751115390374</v>
@@ -40843,13 +40843,13 @@
         <v>139.6945253201055</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>136.3950876495695</v>
+        <v>136.3950876495694</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>131.1440189444677</v>
+        <v>131.1440189444676</v>
       </c>
       <c r="AY199" s="196" t="n">
-        <v>124.2078989819308</v>
+        <v>124.2078989819307</v>
       </c>
       <c r="BA199" s="83" t="inlineStr">
         <is>
@@ -40878,13 +40878,13 @@
         <v>0.5807164183283273</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>0.932950891807051</v>
+        <v>0.9329508918070507</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>1.222751115390387</v>
+        <v>1.222751115390386</v>
       </c>
       <c r="BK199" s="198" t="n">
-        <v>1.507213012102983</v>
+        <v>1.507213012102982</v>
       </c>
       <c r="BL199" s="199" t="n">
         <v>153.0831439719362</v>
@@ -40893,10 +40893,10 @@
         <v>139.6945253201041</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>136.3950876495698</v>
+        <v>136.3950876495697</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>131.1440189444677</v>
+        <v>131.1440189444676</v>
       </c>
       <c r="BP199" s="201" t="n">
         <v>124.2078989819334</v>
@@ -40907,7 +40907,7 @@
         </is>
       </c>
       <c r="BS199" s="335" t="n">
-        <v>69.25540759172317</v>
+        <v>69.25540759172318</v>
       </c>
       <c r="BT199" s="336" t="n">
         <v>56.33223463137914</v>
@@ -40916,40 +40916,40 @@
         <v>55.6562685015753</v>
       </c>
       <c r="BV199" s="336" t="n">
-        <v>51.23859989215607</v>
+        <v>51.23859989215605</v>
       </c>
       <c r="BW199" s="337" t="n">
-        <v>45.51792185462427</v>
+        <v>45.51792185462426</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.4511414436917203</v>
+        <v>0.4511414436917204</v>
       </c>
       <c r="BY199" s="463" t="n">
         <v>0.402546299882707</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.4084440298900071</v>
+        <v>0.4084440298900074</v>
       </c>
       <c r="CA199" s="463" t="n">
         <v>0.3918221554489026</v>
       </c>
       <c r="CB199" s="464" t="n">
-        <v>0.3682217377497509</v>
+        <v>0.368221737749751</v>
       </c>
       <c r="CC199" s="199" t="n">
-        <v>68.77766776617611</v>
+        <v>68.77766776617612</v>
       </c>
       <c r="CD199" s="200" t="n">
         <v>56.00856036265539</v>
       </c>
       <c r="CE199" s="200" t="n">
-        <v>55.48203028764238</v>
+        <v>55.48203028764239</v>
       </c>
       <c r="CF199" s="200" t="n">
-        <v>51.16885634264532</v>
+        <v>51.1688563426453</v>
       </c>
       <c r="CG199" s="201" t="n">
-        <v>45.53730210716161</v>
+        <v>45.5373021071616</v>
       </c>
       <c r="CI199" s="396" t="n">
         <v>0.9999999999992563</v>
@@ -41135,13 +41135,13 @@
         <v>0.006</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>0.2174036809755346</v>
+        <v>0.2174036809755347</v>
       </c>
       <c r="AQ200" s="190" t="n">
         <v>0.3876611034641557</v>
       </c>
       <c r="AR200" s="190" t="n">
-        <v>0.59921922254444</v>
+        <v>0.5992192225444403</v>
       </c>
       <c r="AS200" s="190" t="n">
         <v>0.7980582769577329</v>
@@ -41150,19 +41150,19 @@
         <v>1.006493398598142</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>81.81134515783621</v>
+        <v>81.81134515783623</v>
       </c>
       <c r="AV200" s="190" t="n">
         <v>80.02547690911118</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>82.57063934430933</v>
+        <v>82.57063934430936</v>
       </c>
       <c r="AX200" s="190" t="n">
         <v>85.93817227649708</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>88.91982616880742</v>
+        <v>88.9198261688074</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41191,7 +41191,7 @@
         <v>0.387661103464941</v>
       </c>
       <c r="BI200" s="190" t="n">
-        <v>0.5992192225430596</v>
+        <v>0.5992192225430597</v>
       </c>
       <c r="BJ200" s="190" t="n">
         <v>0.7980582769576968</v>
@@ -41200,19 +41200,19 @@
         <v>1.006493398597256</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>81.8113451578364</v>
+        <v>81.81134515783641</v>
       </c>
       <c r="BM200" s="190" t="n">
         <v>80.02547690911196</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>82.57063934430795</v>
+        <v>82.57063934430798</v>
       </c>
       <c r="BO200" s="190" t="n">
         <v>85.93817227649704</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>88.91982616880654</v>
+        <v>88.91982616880652</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41241,13 +41241,13 @@
         <v>0.2013055634134735</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.2116220374516506</v>
+        <v>0.2116220374516505</v>
       </c>
       <c r="CA200" s="463" t="n">
         <v>0.2217157632383286</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.2241174073297618</v>
+        <v>0.2241174073297619</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>18.83343838345126</v>
@@ -41256,13 +41256,13 @@
         <v>16.09329489872612</v>
       </c>
       <c r="CE200" s="190" t="n">
-        <v>17.45621489350139</v>
+        <v>17.45621489350138</v>
       </c>
       <c r="CF200" s="190" t="n">
         <v>19.03493524529607</v>
       </c>
       <c r="CG200" s="198" t="n">
-        <v>19.91181921135895</v>
+        <v>19.91181921135896</v>
       </c>
       <c r="CI200" s="396" t="n">
         <v>0.9999999997151601</v>
@@ -41311,7 +41311,7 @@
         <v>1.00000000004451</v>
       </c>
       <c r="CY200" s="396" t="n">
-        <v>0.9999999985770909</v>
+        <v>0.9999999985770907</v>
       </c>
       <c r="CZ200" s="397" t="n">
         <v>1.000000000163925</v>
@@ -41320,7 +41320,7 @@
         <v>0.9999999999453315</v>
       </c>
       <c r="DB200" s="397" t="n">
-        <v>0.9999999988372786</v>
+        <v>0.999999998837279</v>
       </c>
       <c r="DC200" s="398" t="n">
         <v>0.999999999405071</v>
@@ -41448,31 +41448,31 @@
         <v>0.006</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>0.1858701062171399</v>
+        <v>0.1858701062171398</v>
       </c>
       <c r="AQ201" s="190" t="n">
-        <v>0.3234085444359152</v>
+        <v>0.323408544435915</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>0.5043520759584802</v>
+        <v>0.5043520759584804</v>
       </c>
       <c r="AS201" s="190" t="n">
-        <v>0.6855770043211663</v>
+        <v>0.6855770043211667</v>
       </c>
       <c r="AT201" s="196" t="n">
         <v>0.9130965906488038</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>76.57497738026133</v>
+        <v>76.57497738026129</v>
       </c>
       <c r="AV201" s="190" t="n">
-        <v>79.52009751394985</v>
+        <v>79.52009751394979</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>82.27397308658476</v>
+        <v>82.27397308658482</v>
       </c>
       <c r="AX201" s="190" t="n">
-        <v>80.73541521496797</v>
+        <v>80.73541521496806</v>
       </c>
       <c r="AY201" s="196" t="n">
         <v>84.7822207008457</v>
@@ -41498,31 +41498,31 @@
         <v>0.006</v>
       </c>
       <c r="BG201" s="197" t="n">
-        <v>0.1858701062180884</v>
+        <v>0.1858701062180883</v>
       </c>
       <c r="BH201" s="190" t="n">
-        <v>0.3234085444365418</v>
+        <v>0.3234085444365417</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>0.5043520759585052</v>
+        <v>0.5043520759585054</v>
       </c>
       <c r="BJ201" s="190" t="n">
-        <v>0.685577004323234</v>
+        <v>0.6855770043232344</v>
       </c>
       <c r="BK201" s="198" t="n">
         <v>0.9130965906491814</v>
       </c>
       <c r="BL201" s="197" t="n">
-        <v>76.57497738026228</v>
+        <v>76.57497738026224</v>
       </c>
       <c r="BM201" s="190" t="n">
-        <v>79.52009751395047</v>
+        <v>79.52009751395042</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>82.27397308658479</v>
+        <v>82.27397308658485</v>
       </c>
       <c r="BO201" s="190" t="n">
-        <v>80.73541521497005</v>
+        <v>80.73541521497013</v>
       </c>
       <c r="BP201" s="198" t="n">
         <v>84.78222070084607</v>
@@ -41545,22 +41545,22 @@
         <v>55.5139983432603</v>
       </c>
       <c r="BW201" s="337" t="n">
-        <v>55.46093120356362</v>
+        <v>55.46093120356361</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.5476011357906756</v>
+        <v>0.5476011357906759</v>
       </c>
       <c r="BY201" s="463" t="n">
-        <v>0.5864807639926879</v>
+        <v>0.5864807639926883</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.6166436495693148</v>
+        <v>0.6166436495693144</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.6932064406735403</v>
+        <v>0.6932064406735396</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.6609797701608654</v>
+        <v>0.6609797701608653</v>
       </c>
       <c r="CC201" s="197" t="n">
         <v>41.89126231740506</v>
@@ -41608,10 +41608,10 @@
         <v>0.9999999068006115</v>
       </c>
       <c r="CT201" s="422" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU201" s="423" t="n">
         <v>0.9999999999999999</v>
-      </c>
-      <c r="CU201" s="423" t="n">
-        <v>1</v>
       </c>
       <c r="CV201" s="423" t="n">
         <v>1</v>
@@ -41623,10 +41623,10 @@
         <v>1</v>
       </c>
       <c r="CY201" s="422" t="n">
-        <v>1.000000006826308</v>
+        <v>1.000000006826307</v>
       </c>
       <c r="CZ201" s="423" t="n">
-        <v>1.000000016316011</v>
+        <v>1.00000001631601</v>
       </c>
       <c r="DA201" s="423" t="n">
         <v>0.9999999865923039</v>
@@ -41775,19 +41775,19 @@
         <v>0</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="AW202" s="209" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41825,19 +41825,19 @@
         <v>0</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>3.005182788725758</v>
+        <v>3.005182788725762</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>2.227141504817261</v>
+        <v>2.227141504817258</v>
       </c>
       <c r="BN202" s="212" t="n">
         <v>2.294824335148661</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>2.341363372665477</v>
+        <v>2.34136337266548</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>2.388846221863133</v>
+        <v>2.38884622186313</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41860,19 +41860,19 @@
         <v>2.388846221863131</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.7217567347449492</v>
+        <v>0.7217567347449483</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>1.000000000000001</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="BZ202" s="467" t="n">
         <v>0.9999999999999992</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.999999999999999</v>
+        <v>0.9999999999999976</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>0.9999999999999989</v>
+        <v>1</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>2.164511354735448</v>
@@ -41943,7 +41943,7 @@
         <v>306.259651823</v>
       </c>
       <c r="O203" s="215" t="n">
-        <v>308.3745962560001</v>
+        <v>308.374596256</v>
       </c>
       <c r="P203" s="215" t="n">
         <v>305.04373089</v>
@@ -41993,7 +41993,7 @@
         <v>306.259651823</v>
       </c>
       <c r="AF203" s="218" t="n">
-        <v>308.3745962560001</v>
+        <v>308.374596256</v>
       </c>
       <c r="AG203" s="218" t="n">
         <v>305.04373089</v>
@@ -42025,7 +42025,7 @@
         <v>0.7403799008836744</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>1.291786066229837</v>
+        <v>1.291786066229836</v>
       </c>
       <c r="AR203" s="207" t="n">
         <v>2.036522190309678</v>
@@ -42072,7 +42072,7 @@
         <v>0.018</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>0.7403799008843013</v>
+        <v>0.7403799008843012</v>
       </c>
       <c r="BH203" s="222" t="n">
         <v>1.29178606622981</v>
@@ -42081,16 +42081,16 @@
         <v>2.036522190308616</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>2.706386396671317</v>
+        <v>2.706386396671318</v>
       </c>
       <c r="BK203" s="214" t="n">
-        <v>3.42680300134942</v>
+        <v>3.426803001349419</v>
       </c>
       <c r="BL203" s="222" t="n">
         <v>314.4746492987607</v>
       </c>
       <c r="BM203" s="222" t="n">
-        <v>301.4672412479838</v>
+        <v>301.4672412479837</v>
       </c>
       <c r="BN203" s="222" t="n">
         <v>303.5345244156112</v>
@@ -42099,7 +42099,7 @@
         <v>300.1589698086003</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>300.2987920734492</v>
+        <v>300.2987920734491</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="BS203" s="271" t="n">
-        <v>132.1712390308412</v>
+        <v>132.1712390308413</v>
       </c>
       <c r="BT203" s="272" t="n">
         <v>121.1337260431404</v>
@@ -42116,25 +42116,25 @@
         <v>125.8143879751312</v>
       </c>
       <c r="BV203" s="272" t="n">
-        <v>128.0366376123743</v>
+        <v>128.0366376123742</v>
       </c>
       <c r="BW203" s="273" t="n">
         <v>123.1276364700726</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.4197687492784518</v>
+        <v>0.4197687492784519</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.4020516283175345</v>
+        <v>0.4020516283175347</v>
       </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.4158147704275203</v>
+        <v>0.4158147704275204</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.4289762800406604</v>
+        <v>0.4289762800406602</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.4132833896497346</v>
+        <v>0.4132833896497347</v>
       </c>
       <c r="CC203" s="212" t="n">
         <v>131.6668798217679</v>
@@ -42943,13 +42943,13 @@
         <v>0.2813335157534056</v>
       </c>
       <c r="AR208" s="463" t="n">
-        <v>0.4192100015235481</v>
+        <v>0.4192100015235483</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.4687337995696746</v>
+        <v>0.4687337995696748</v>
       </c>
       <c r="AT208" s="474" t="n">
-        <v>0.5115460721818801</v>
+        <v>0.5115460721818802</v>
       </c>
       <c r="AU208" s="463" t="n">
         <v>0.09178067228700051</v>
@@ -42958,13 +42958,13 @@
         <v>0.2783335157509286</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.4152100015238629</v>
+        <v>0.4152100015238631</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.4637337995696846</v>
+        <v>0.4637337995696847</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.5055460721836441</v>
+        <v>0.5055460721836442</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42993,13 +42993,13 @@
         <v>0.2813335157516255</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.4192100015237309</v>
+        <v>0.4192100015237311</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.4687337995696799</v>
+        <v>0.46873379956968</v>
       </c>
       <c r="BK208" s="464" t="n">
-        <v>0.5115460721827417</v>
+        <v>0.5115460721827418</v>
       </c>
       <c r="BL208" s="475" t="n">
         <v>0.09178067228530568</v>
@@ -43008,13 +43008,13 @@
         <v>0.2783335157533216</v>
       </c>
       <c r="BN208" s="476" t="n">
-        <v>0.4152100015229037</v>
+        <v>0.4152100015229039</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.4637337995712763</v>
+        <v>0.4637337995712764</v>
       </c>
       <c r="BP208" s="477" t="n">
-        <v>0.5055460721831517</v>
+        <v>0.5055460721831518</v>
       </c>
       <c r="BR208" s="83" t="inlineStr">
         <is>
@@ -43043,13 +43043,13 @@
         <v>0.2791393690116816</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.4162049352672902</v>
+        <v>0.4162049352672904</v>
       </c>
       <c r="CA208" s="463" t="n">
-        <v>0.4647828613116529</v>
+        <v>0.464782861311653</v>
       </c>
       <c r="CB208" s="464" t="n">
-        <v>0.5066346541436435</v>
+        <v>0.5066346541436436</v>
       </c>
       <c r="CC208" s="478" t="n">
         <v>0</v>
@@ -43177,7 +43177,7 @@
         </is>
       </c>
       <c r="AK209" s="233" t="n">
-        <v>26.89049533002447</v>
+        <v>26.89049533002446</v>
       </c>
       <c r="AL209" s="190" t="n">
         <v>49.19489091253585</v>
@@ -43192,28 +43192,28 @@
         <v>78.82907359740186</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.249378473163545</v>
+        <v>0.2493784731635449</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.3837053929785563</v>
+        <v>0.3837053929785562</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.4528118121865785</v>
+        <v>0.4528118121865784</v>
       </c>
       <c r="AS209" s="463" t="n">
         <v>0.4665795941362777</v>
       </c>
       <c r="AT209" s="474" t="n">
-        <v>0.4759230439504751</v>
+        <v>0.475923043950475</v>
       </c>
       <c r="AU209" s="463" t="n">
-        <v>0.247378473164404</v>
+        <v>0.2473784731644039</v>
       </c>
       <c r="AV209" s="463" t="n">
         <v>0.3807053929805823</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.4488118121842746</v>
+        <v>0.4488118121842744</v>
       </c>
       <c r="AX209" s="463" t="n">
         <v>0.4615795941362325</v>
@@ -43242,13 +43242,13 @@
         <v>78.82907359699999</v>
       </c>
       <c r="BG209" s="462" t="n">
-        <v>0.2493784731641898</v>
+        <v>0.2493784731641897</v>
       </c>
       <c r="BH209" s="463" t="n">
         <v>0.3837053929798049</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.4528118121853177</v>
+        <v>0.4528118121853176</v>
       </c>
       <c r="BJ209" s="463" t="n">
         <v>0.4665795941362536</v>
@@ -43263,7 +43263,7 @@
         <v>0.3807053929834029</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.4488118121822675</v>
+        <v>0.4488118121822673</v>
       </c>
       <c r="BO209" s="463" t="n">
         <v>0.4615795941359886</v>
@@ -43450,13 +43450,13 @@
         <v>0.1780377293721049</v>
       </c>
       <c r="AQ210" s="463" t="n">
-        <v>0.2653562467777616</v>
+        <v>0.2653562467777617</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.35148778079099</v>
+        <v>0.3514877807909899</v>
       </c>
       <c r="AS210" s="463" t="n">
-        <v>0.4161863823750239</v>
+        <v>0.4161863823750236</v>
       </c>
       <c r="AT210" s="474" t="n">
         <v>0.4488920998997264</v>
@@ -43465,13 +43465,13 @@
         <v>0.1760377293772077</v>
       </c>
       <c r="AV210" s="463" t="n">
-        <v>0.2623562467796991</v>
+        <v>0.2623562467796993</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.3474877807910395</v>
+        <v>0.3474877807910394</v>
       </c>
       <c r="AX210" s="463" t="n">
-        <v>0.4111863823780398</v>
+        <v>0.4111863823780396</v>
       </c>
       <c r="AY210" s="474" t="n">
         <v>0.4428920999001399</v>
@@ -43500,28 +43500,28 @@
         <v>0.1780377293762992</v>
       </c>
       <c r="BH210" s="463" t="n">
-        <v>0.265356246779185</v>
+        <v>0.2653562467791851</v>
       </c>
       <c r="BI210" s="463" t="n">
-        <v>0.3514877807910221</v>
+        <v>0.351487780791022</v>
       </c>
       <c r="BJ210" s="463" t="n">
-        <v>0.4161863823767846</v>
+        <v>0.4161863823767843</v>
       </c>
       <c r="BK210" s="464" t="n">
         <v>0.4488920998999543</v>
       </c>
       <c r="BL210" s="462" t="n">
-        <v>0.1760377293786459</v>
+        <v>0.176037729378646</v>
       </c>
       <c r="BM210" s="463" t="n">
-        <v>0.2623562467832344</v>
+        <v>0.2623562467832345</v>
       </c>
       <c r="BN210" s="463" t="n">
-        <v>0.347487780790693</v>
+        <v>0.3474877807906929</v>
       </c>
       <c r="BO210" s="463" t="n">
-        <v>0.411186382379142</v>
+        <v>0.4111863823791417</v>
       </c>
       <c r="BP210" s="464" t="n">
         <v>0.442892099897649</v>
@@ -43547,16 +43547,16 @@
         <v>0</v>
       </c>
       <c r="BX210" s="462" t="n">
-        <v>0.1761806443946909</v>
+        <v>0.176180644394691</v>
       </c>
       <c r="BY210" s="463" t="n">
-        <v>0.2625407780098296</v>
+        <v>0.2625407780098297</v>
       </c>
       <c r="BZ210" s="463" t="n">
-        <v>0.3476955335033973</v>
+        <v>0.3476955335033972</v>
       </c>
       <c r="CA210" s="463" t="n">
-        <v>0.411412610188594</v>
+        <v>0.4114126101885937</v>
       </c>
       <c r="CB210" s="464" t="n">
         <v>0.4431103396770386</v>
@@ -43869,7 +43869,7 @@
         <v>0.4456361163304386</v>
       </c>
       <c r="L212" s="496" t="n">
-        <v>0.4755947700452124</v>
+        <v>0.4755947700452125</v>
       </c>
       <c r="M212" s="495" t="n">
         <v>0.1486428264486221</v>
@@ -43881,10 +43881,10 @@
         <v>0.399050242938167</v>
       </c>
       <c r="P212" s="495" t="n">
-        <v>0.4406575824926322</v>
+        <v>0.4406575824926321</v>
       </c>
       <c r="Q212" s="496" t="n">
-        <v>0.4696196943955238</v>
+        <v>0.4696196943955239</v>
       </c>
       <c r="S212" s="143" t="inlineStr">
         <is>
@@ -43919,7 +43919,7 @@
         <v>0.4456361163304386</v>
       </c>
       <c r="AC212" s="499" t="n">
-        <v>0.4755947700452124</v>
+        <v>0.4755947700452125</v>
       </c>
       <c r="AD212" s="498" t="n">
         <v>0.1486428264486221</v>
@@ -43931,10 +43931,10 @@
         <v>0.399050242938167</v>
       </c>
       <c r="AG212" s="498" t="n">
-        <v>0.4406575824926322</v>
+        <v>0.4406575824926321</v>
       </c>
       <c r="AH212" s="499" t="n">
-        <v>0.4696196943955238</v>
+        <v>0.4696196943955239</v>
       </c>
       <c r="AJ212" s="150" t="inlineStr">
         <is>
@@ -43969,22 +43969,22 @@
         <v>0.4528285823116924</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.4823709688590629</v>
+        <v>0.4823709688590631</v>
       </c>
       <c r="AU212" s="501" t="n">
         <v>0.1573452564180099</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.3034852776902638</v>
+        <v>0.303485277690264</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.4064930269674435</v>
+        <v>0.4064930269674434</v>
       </c>
       <c r="AX212" s="501" t="n">
         <v>0.4478501172921799</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.476395960159035</v>
+        <v>0.4763959601590351</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>273.223887706</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.1593291512625773</v>
+        <v>0.1593291512625774</v>
       </c>
       <c r="BH212" s="504" t="n">
         <v>0.3064698408205093</v>
@@ -44019,13 +44019,13 @@
         <v>0.4528285823113519</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.4823709688587616</v>
+        <v>0.4823709688587617</v>
       </c>
       <c r="BL212" s="504" t="n">
         <v>0.1573452564175661</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.3034852776931115</v>
+        <v>0.3034852776931116</v>
       </c>
       <c r="BN212" s="504" t="n">
         <v>0.4064930269663046</v>
@@ -44057,10 +44057,10 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.1576872440947847</v>
+        <v>0.1576872440947848</v>
       </c>
       <c r="BY212" s="504" t="n">
-        <v>0.3039922756524474</v>
+        <v>0.3039922756524475</v>
       </c>
       <c r="BZ212" s="504" t="n">
         <v>0.4070680379581978</v>
@@ -44737,13 +44737,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN219" s="368" t="n">
         <v>77145.27984093782</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>89580.48173789639</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>588.3746268688296</v>
@@ -44752,13 +44752,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="AR219" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS219" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44772,13 +44772,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE219" s="375" t="n">
         <v>77145.27984093782</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>89580.48173789639</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44787,13 +44787,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BI219" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ219" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44807,13 +44807,13 @@
         <v>34145.19060566285</v>
       </c>
       <c r="BU219" s="375" t="n">
-        <v>61761.25223350792</v>
+        <v>61761.25223350793</v>
       </c>
       <c r="BV219" s="375" t="n">
         <v>76322.36841565622</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>88529.77893785876</v>
+        <v>88529.77893785873</v>
       </c>
       <c r="BX219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44822,13 +44822,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BZ219" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA219" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI219" s="199" t="n">
         <v>0</v>
@@ -44935,7 +44935,7 @@
         <v>128629.5373619414</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>144792.812781395</v>
+        <v>144792.8127813951</v>
       </c>
       <c r="AO220" s="380" t="n">
         <v>159406.5384542814</v>
@@ -44950,7 +44950,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="AS220" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="AT220" s="382" t="n">
         <v>1996.685743614349</v>
@@ -44970,7 +44970,7 @@
         <v>128629.5373619414</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>144792.812781395</v>
+        <v>144792.8127813951</v>
       </c>
       <c r="BF220" s="392" t="n">
         <v>159406.5384542814</v>
@@ -44985,7 +44985,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="BJ220" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="BK220" s="387" t="n">
         <v>1996.685743614349</v>
@@ -45020,7 +45020,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="CA220" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="CB220" s="387" t="n">
         <v>1996.685743614349</v>
@@ -45127,7 +45127,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>74511.52994761143</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="AN221" s="368" t="n">
         <v>88747.26377651544</v>
@@ -45162,7 +45162,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>74511.52994761143</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="BE221" s="375" t="n">
         <v>88747.26377651544</v>
@@ -45197,7 +45197,7 @@
         <v>49256.43254092836</v>
       </c>
       <c r="BU221" s="375" t="n">
-        <v>73663.57409792523</v>
+        <v>73663.57409792522</v>
       </c>
       <c r="BV221" s="375" t="n">
         <v>87681.06762627322</v>
@@ -45517,10 +45517,10 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="AN223" s="408" t="n">
-        <v>310685.3563988483</v>
+        <v>310685.3563988484</v>
       </c>
       <c r="AO223" s="409" t="n">
         <v>361266.5879902404</v>
@@ -45532,7 +45532,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="AS223" s="437" t="n">
         <v>1262.096640327373</v>
@@ -45552,10 +45552,10 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="BE223" s="440" t="n">
-        <v>310685.3563988483</v>
+        <v>310685.3563988484</v>
       </c>
       <c r="BF223" s="441" t="n">
         <v>361266.5879902404</v>
@@ -45567,7 +45567,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="BJ223" s="443" t="n">
         <v>1262.096640327373</v>
@@ -45581,7 +45581,7 @@
         </is>
       </c>
       <c r="BS223" s="439" t="n">
-        <v>79935.96700424918</v>
+        <v>79935.96700424916</v>
       </c>
       <c r="BT223" s="440" t="n">
         <v>172764.2669635623</v>
@@ -45593,7 +45593,7 @@
         <v>307244.6077463383</v>
       </c>
       <c r="BW223" s="441" t="n">
-        <v>356705.4784037997</v>
+        <v>356705.4784037996</v>
       </c>
       <c r="BX223" s="442" t="n">
         <v>1361.296121074501</v>
@@ -47635,13 +47635,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN237" s="368" t="n">
         <v>77145.27984093782</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>89580.48173789639</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>588.3746268688296</v>
@@ -47650,13 +47650,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="AR237" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS237" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47670,13 +47670,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>62356.24033128739</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE237" s="375" t="n">
         <v>77145.27984093782</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>89580.48173789639</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47685,13 +47685,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BI237" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ237" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47705,13 +47705,13 @@
         <v>34145.19060566285</v>
       </c>
       <c r="BU237" s="375" t="n">
-        <v>61761.25223350792</v>
+        <v>61761.25223350793</v>
       </c>
       <c r="BV237" s="375" t="n">
         <v>76322.36841565622</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>88529.77893785876</v>
+        <v>88529.77893785873</v>
       </c>
       <c r="BX237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47720,13 +47720,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BZ237" s="372" t="n">
-        <v>637.7485705640687</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA237" s="372" t="n">
         <v>672.9999385701529</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>697.1163277335224</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI237" s="199" t="n">
         <v>0</v>
@@ -47833,7 +47833,7 @@
         <v>128629.5373619414</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>144792.812781395</v>
+        <v>144792.8127813951</v>
       </c>
       <c r="AO238" s="380" t="n">
         <v>159406.5384542814</v>
@@ -47848,7 +47848,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="AS238" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="AT238" s="382" t="n">
         <v>1996.685743614349</v>
@@ -47868,7 +47868,7 @@
         <v>128629.5373619414</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>144792.812781395</v>
+        <v>144792.8127813951</v>
       </c>
       <c r="BF238" s="392" t="n">
         <v>159406.5384542814</v>
@@ -47883,7 +47883,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="BJ238" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="BK238" s="387" t="n">
         <v>1996.685743614349</v>
@@ -47918,7 +47918,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="CA238" s="372" t="n">
-        <v>1944.270389399368</v>
+        <v>1944.270389399369</v>
       </c>
       <c r="CB238" s="387" t="n">
         <v>1996.685743614349</v>
@@ -48025,7 +48025,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>74511.52994761143</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="AN239" s="368" t="n">
         <v>88747.26377651544</v>
@@ -48060,7 +48060,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>74511.52994761143</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="BE239" s="375" t="n">
         <v>88747.26377651544</v>
@@ -48095,7 +48095,7 @@
         <v>49256.43254092836</v>
       </c>
       <c r="BU239" s="375" t="n">
-        <v>73663.57409792523</v>
+        <v>73663.57409792522</v>
       </c>
       <c r="BV239" s="375" t="n">
         <v>87681.06762627322</v>
@@ -48415,10 +48415,10 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="AN241" s="408" t="n">
-        <v>310685.3563988483</v>
+        <v>310685.3563988484</v>
       </c>
       <c r="AO241" s="409" t="n">
         <v>361266.5879902404</v>
@@ -48430,7 +48430,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="AS241" s="437" t="n">
         <v>1262.096640327373</v>
@@ -48450,10 +48450,10 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>265497.3076408402</v>
+        <v>265497.3076408403</v>
       </c>
       <c r="BE241" s="440" t="n">
-        <v>310685.3563988483</v>
+        <v>310685.3563988484</v>
       </c>
       <c r="BF241" s="441" t="n">
         <v>361266.5879902404</v>
@@ -48465,7 +48465,7 @@
         <v>1314.765281734809</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>1264.710304505289</v>
+        <v>1264.71030450529</v>
       </c>
       <c r="BJ241" s="443" t="n">
         <v>1262.096640327373</v>
@@ -48479,7 +48479,7 @@
         </is>
       </c>
       <c r="BS241" s="439" t="n">
-        <v>79935.96700424918</v>
+        <v>79935.96700424916</v>
       </c>
       <c r="BT241" s="440" t="n">
         <v>172764.2669635623</v>
@@ -48491,7 +48491,7 @@
         <v>307244.6077463383</v>
       </c>
       <c r="BW241" s="441" t="n">
-        <v>356705.4784037997</v>
+        <v>356705.4784037996</v>
       </c>
       <c r="BX241" s="442" t="n">
         <v>1361.296121074501</v>
@@ -49036,13 +49036,13 @@
         </is>
       </c>
       <c r="AK246" s="506" t="n">
-        <v>113879.8966047299</v>
+        <v>113879.89660473</v>
       </c>
       <c r="AL246" s="368" t="n">
         <v>111313.9371345226</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>115621.2447413</v>
+        <v>115621.2447412999</v>
       </c>
       <c r="AN246" s="368" t="n">
         <v>117930.9315359258</v>
@@ -49051,19 +49051,19 @@
         <v>120363.4657088642</v>
       </c>
       <c r="AP246" s="381" t="n">
-        <v>745.5505766414578</v>
+        <v>745.5505766414586</v>
       </c>
       <c r="AQ246" s="372" t="n">
         <v>800.1645416303618</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>853.5318245326973</v>
+        <v>853.531824532697</v>
       </c>
       <c r="AS246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>980.9518566040676</v>
+        <v>980.9518566040679</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49071,13 +49071,13 @@
         </is>
       </c>
       <c r="BB246" s="391" t="n">
-        <v>113879.8966047299</v>
+        <v>113879.89660473</v>
       </c>
       <c r="BC246" s="375" t="n">
         <v>111313.9371345226</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>115621.2447413</v>
+        <v>115621.2447412999</v>
       </c>
       <c r="BE246" s="375" t="n">
         <v>117930.9315359258</v>
@@ -49086,19 +49086,19 @@
         <v>120363.4657088642</v>
       </c>
       <c r="BG246" s="386" t="n">
-        <v>745.5505766414578</v>
+        <v>745.5505766414586</v>
       </c>
       <c r="BH246" s="372" t="n">
         <v>800.1645416303618</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>853.5318245326973</v>
+        <v>853.531824532697</v>
       </c>
       <c r="BJ246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>980.9518566040676</v>
+        <v>980.9518566040679</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         </is>
       </c>
       <c r="BS246" s="391" t="n">
-        <v>113661.0936105531</v>
+        <v>113661.0936105532</v>
       </c>
       <c r="BT246" s="375" t="n">
         <v>111331.4519176831</v>
@@ -49121,19 +49121,19 @@
         <v>121312.5040357627</v>
       </c>
       <c r="BX246" s="386" t="n">
-        <v>745.5505766414578</v>
+        <v>745.5505766414586</v>
       </c>
       <c r="BY246" s="372" t="n">
         <v>800.1645416303618</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>853.5318245326973</v>
+        <v>853.531824532697</v>
       </c>
       <c r="CA246" s="372" t="n">
         <v>907.7107505689086</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>980.9518566040676</v>
+        <v>980.9518566040679</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49224,10 +49224,10 @@
         <v>195568.7596927182</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>214940.2738774986</v>
+        <v>214940.2738774985</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>235525.5846029741</v>
+        <v>235525.5846029742</v>
       </c>
       <c r="AP247" s="381" t="n">
         <v>2114.762873860429</v>
@@ -49236,13 +49236,13 @@
         <v>2255.25882410995</v>
       </c>
       <c r="AR247" s="372" t="n">
-        <v>2385.816415058427</v>
+        <v>2385.816415058426</v>
       </c>
       <c r="AS247" s="372" t="n">
-        <v>2524.547640111201</v>
+        <v>2524.5476401112</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>2679.065588596888</v>
+        <v>2679.065588596889</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49259,10 +49259,10 @@
         <v>195568.7596927182</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>214940.2738774986</v>
+        <v>214940.2738774985</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>235525.5846029741</v>
+        <v>235525.5846029742</v>
       </c>
       <c r="BG247" s="386" t="n">
         <v>2114.762873860429</v>
@@ -49271,13 +49271,13 @@
         <v>2255.25882410995</v>
       </c>
       <c r="BI247" s="372" t="n">
-        <v>2385.816415058427</v>
+        <v>2385.816415058426</v>
       </c>
       <c r="BJ247" s="372" t="n">
-        <v>2524.547640111201</v>
+        <v>2524.5476401112</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>2679.065588596888</v>
+        <v>2679.065588596889</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49297,7 +49297,7 @@
         <v>216739.6677239698</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>238022.8751124912</v>
+        <v>238022.8751124913</v>
       </c>
       <c r="BX247" s="386" t="n">
         <v>2114.762873860429</v>
@@ -49306,13 +49306,13 @@
         <v>2255.25882410995</v>
       </c>
       <c r="BZ247" s="372" t="n">
-        <v>2385.816415058427</v>
+        <v>2385.816415058426</v>
       </c>
       <c r="CA247" s="372" t="n">
-        <v>2524.547640111201</v>
+        <v>2524.5476401112</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>2679.065588596888</v>
+        <v>2679.065588596889</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49394,7 +49394,7 @@
         </is>
       </c>
       <c r="AK248" s="506" t="n">
-        <v>157813.7661646546</v>
+        <v>157813.7661646547</v>
       </c>
       <c r="AL248" s="368" t="n">
         <v>174261.8891516261</v>
@@ -49403,25 +49403,25 @@
         <v>197065.9005779591</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>220633.9572179477</v>
+        <v>220633.9572179478</v>
       </c>
       <c r="AO248" s="380" t="n">
-        <v>248391.8019773486</v>
+        <v>248391.8019773487</v>
       </c>
       <c r="AP248" s="381" t="n">
-        <v>2065.919759980865</v>
+        <v>2065.919759980866</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2200.368366660348</v>
+        <v>2200.368366660347</v>
       </c>
       <c r="AR248" s="372" t="n">
         <v>2410.013622954898</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2756.207409643825</v>
+        <v>2756.207409643827</v>
       </c>
       <c r="AT248" s="382" t="n">
-        <v>2961.659664545513</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="BA248" s="111" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         </is>
       </c>
       <c r="BB248" s="391" t="n">
-        <v>157813.7661646546</v>
+        <v>157813.7661646547</v>
       </c>
       <c r="BC248" s="375" t="n">
         <v>174261.8891516261</v>
@@ -49438,25 +49438,25 @@
         <v>197065.9005779591</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>220633.9572179477</v>
+        <v>220633.9572179478</v>
       </c>
       <c r="BF248" s="392" t="n">
-        <v>248391.8019773486</v>
+        <v>248391.8019773487</v>
       </c>
       <c r="BG248" s="386" t="n">
-        <v>2065.919759980865</v>
+        <v>2065.919759980866</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2200.368366660348</v>
+        <v>2200.368366660347</v>
       </c>
       <c r="BI248" s="372" t="n">
         <v>2410.013622954898</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2756.207409643825</v>
+        <v>2756.207409643827</v>
       </c>
       <c r="BK248" s="387" t="n">
-        <v>2961.659664545513</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="BR248" s="111" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>158042.0144071814</v>
+        <v>158042.0144071815</v>
       </c>
       <c r="BT248" s="375" t="n">
         <v>174806.782848244</v>
@@ -49473,25 +49473,25 @@
         <v>198099.827282697</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>222315.7395968188</v>
+        <v>222315.7395968189</v>
       </c>
       <c r="BW248" s="392" t="n">
         <v>250874.0988206002</v>
       </c>
       <c r="BX248" s="386" t="n">
-        <v>2065.919759980865</v>
+        <v>2065.919759980866</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2200.368366660348</v>
+        <v>2200.368366660347</v>
       </c>
       <c r="BZ248" s="372" t="n">
         <v>2410.013622954898</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2756.207409643825</v>
+        <v>2756.207409643827</v>
       </c>
       <c r="CB248" s="387" t="n">
-        <v>2961.659664545513</v>
+        <v>2961.659664545514</v>
       </c>
       <c r="CI248" s="225" t="n"/>
       <c r="CJ248" s="225" t="n"/>
@@ -49576,13 +49576,13 @@
         <v>56453.6925031906</v>
       </c>
       <c r="AL249" s="408" t="n">
-        <v>5802.278701392584</v>
+        <v>5802.278701392701</v>
       </c>
       <c r="AM249" s="408" t="n">
         <v>6277.540448684362</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>6725.091417432879</v>
+        <v>6725.091417432937</v>
       </c>
       <c r="AO249" s="409" t="n">
         <v>7204.550084947259</v>
@@ -49591,13 +49591,13 @@
         <v>18785.44383717041</v>
       </c>
       <c r="AQ249" s="411" t="n">
-        <v>2605.258214786213</v>
+        <v>2605.258214786265</v>
       </c>
       <c r="AR249" s="411" t="n">
         <v>2735.521125927209</v>
       </c>
       <c r="AS249" s="411" t="n">
-        <v>2872.297182853888</v>
+        <v>2872.297182853913</v>
       </c>
       <c r="AT249" s="412" t="n">
         <v>3015.912040966551</v>
@@ -49611,13 +49611,13 @@
         <v>56453.6925031906</v>
       </c>
       <c r="BC249" s="420" t="n">
-        <v>5802.278701392584</v>
+        <v>5802.278701392701</v>
       </c>
       <c r="BD249" s="420" t="n">
         <v>6277.540448684362</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>6725.091417432879</v>
+        <v>6725.091417432937</v>
       </c>
       <c r="BF249" s="421" t="n">
         <v>7204.550084947259</v>
@@ -49626,13 +49626,13 @@
         <v>18785.44383717041</v>
       </c>
       <c r="BH249" s="417" t="n">
-        <v>2605.258214786213</v>
+        <v>2605.258214786265</v>
       </c>
       <c r="BI249" s="417" t="n">
         <v>2735.521125927209</v>
       </c>
       <c r="BJ249" s="417" t="n">
-        <v>2872.297182853888</v>
+        <v>2872.297182853913</v>
       </c>
       <c r="BK249" s="418" t="n">
         <v>3015.912040966551</v>
@@ -49646,28 +49646,28 @@
         <v>56336.58064497267</v>
       </c>
       <c r="BT249" s="420" t="n">
-        <v>5785.615091863503</v>
+        <v>5785.61509186362</v>
       </c>
       <c r="BU249" s="420" t="n">
         <v>6259.511931230557</v>
       </c>
       <c r="BV249" s="420" t="n">
-        <v>6705.777574855722</v>
+        <v>6705.777574855781</v>
       </c>
       <c r="BW249" s="421" t="n">
-        <v>7183.859281277409</v>
+        <v>7183.85928127741</v>
       </c>
       <c r="BX249" s="416" t="n">
         <v>18785.44383717041</v>
       </c>
       <c r="BY249" s="417" t="n">
-        <v>2605.258214786213</v>
+        <v>2605.258214786265</v>
       </c>
       <c r="BZ249" s="417" t="n">
         <v>2735.521125927209</v>
       </c>
       <c r="CA249" s="417" t="n">
-        <v>2872.297182853888</v>
+        <v>2872.297182853913</v>
       </c>
       <c r="CB249" s="418" t="n">
         <v>3015.912040966551</v>
@@ -49709,7 +49709,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="L250" s="428" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="S250" s="143" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="AC250" s="434" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="AJ250" s="150" t="inlineStr">
         <is>
@@ -49752,19 +49752,19 @@
         </is>
       </c>
       <c r="AK250" s="435" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400754</v>
       </c>
       <c r="AL250" s="408" t="n">
         <v>470981.9918168656</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>514533.4454606617</v>
+        <v>514533.4454606615</v>
       </c>
       <c r="AN250" s="408" t="n">
         <v>560230.254048805</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>611485.4023741342</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="AP250" s="436" t="n">
         <v>1595.934018941659</v>
@@ -49779,7 +49779,7 @@
         <v>1883.427091547001</v>
       </c>
       <c r="AT250" s="438" t="n">
-        <v>2059.761192982849</v>
+        <v>2059.76119298285</v>
       </c>
       <c r="BA250" s="155" t="inlineStr">
         <is>
@@ -49787,19 +49787,19 @@
         </is>
       </c>
       <c r="BB250" s="439" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400754</v>
       </c>
       <c r="BC250" s="440" t="n">
         <v>470981.9918168656</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>514533.4454606617</v>
+        <v>514533.4454606615</v>
       </c>
       <c r="BE250" s="440" t="n">
         <v>560230.254048805</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>611485.4023741342</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="BG250" s="442" t="n">
         <v>1595.934018941659</v>
@@ -49814,7 +49814,7 @@
         <v>1883.427091547001</v>
       </c>
       <c r="BK250" s="444" t="n">
-        <v>2059.761192982849</v>
+        <v>2059.76119298285</v>
       </c>
       <c r="BR250" s="155" t="inlineStr">
         <is>
@@ -49822,22 +49822,22 @@
         </is>
       </c>
       <c r="BS250" s="439" t="n">
-        <v>500845.7947322577</v>
+        <v>500845.7947322579</v>
       </c>
       <c r="BT250" s="440" t="n">
         <v>472219.6385785875</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>517101.5044096496</v>
+        <v>517101.5044096495</v>
       </c>
       <c r="BV250" s="440" t="n">
         <v>564300.9875857062</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>617393.3372501315</v>
+        <v>617393.3372501316</v>
       </c>
       <c r="BX250" s="442" t="n">
-        <v>1596.752449216095</v>
+        <v>1596.752449216096</v>
       </c>
       <c r="BY250" s="443" t="n">
         <v>1570.164229808746</v>
@@ -49846,10 +49846,10 @@
         <v>1707.66459319838</v>
       </c>
       <c r="CA250" s="443" t="n">
-        <v>1884.523741337633</v>
+        <v>1884.523741337634</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>2060.705553829281</v>
+        <v>2060.705553829282</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51942,13 +51942,13 @@
         </is>
       </c>
       <c r="AK264" s="506" t="n">
-        <v>113879.8966047299</v>
+        <v>113879.89660473</v>
       </c>
       <c r="AL264" s="368" t="n">
         <v>111313.9371345226</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>115621.2447413</v>
+        <v>115621.2447412999</v>
       </c>
       <c r="AN264" s="368" t="n">
         <v>117930.9315359258</v>
@@ -51957,19 +51957,19 @@
         <v>120363.4657088642</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>745.5505766402584</v>
+        <v>745.5505766402592</v>
       </c>
       <c r="AQ264" s="372" t="n">
         <v>800.1645416316516</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>853.5318245278913</v>
+        <v>853.5318245278914</v>
       </c>
       <c r="AS264" s="372" t="n">
-        <v>907.7107505683687</v>
+        <v>907.7107505683691</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>980.951856605423</v>
+        <v>980.9518566054237</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51977,13 +51977,13 @@
         </is>
       </c>
       <c r="BB264" s="391" t="n">
-        <v>113879.8966047299</v>
+        <v>113879.89660473</v>
       </c>
       <c r="BC264" s="375" t="n">
         <v>111313.9371345226</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>115621.2447413</v>
+        <v>115621.2447412999</v>
       </c>
       <c r="BE264" s="375" t="n">
         <v>117930.9315359258</v>
@@ -51992,19 +51992,19 @@
         <v>120363.4657088642</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>745.5505766402584</v>
+        <v>745.5505766402592</v>
       </c>
       <c r="BH264" s="372" t="n">
         <v>800.1645416316516</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>853.5318245278913</v>
+        <v>853.5318245278914</v>
       </c>
       <c r="BJ264" s="372" t="n">
-        <v>907.7107505683687</v>
+        <v>907.7107505683691</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>980.951856605423</v>
+        <v>980.9518566054237</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52012,34 +52012,34 @@
         </is>
       </c>
       <c r="BS264" s="391" t="n">
-        <v>113661.0936105531</v>
+        <v>113661.0936105533</v>
       </c>
       <c r="BT264" s="375" t="n">
         <v>111331.4519176831</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>115941.6592591056</v>
+        <v>115941.6592591055</v>
       </c>
       <c r="BV264" s="375" t="n">
         <v>118539.8026900617</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>121312.5040357627</v>
+        <v>121312.5040357628</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>745.5505766402584</v>
+        <v>745.5505766402592</v>
       </c>
       <c r="BY264" s="372" t="n">
         <v>800.1645416316516</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>853.5318245278913</v>
+        <v>853.5318245278914</v>
       </c>
       <c r="CA264" s="372" t="n">
-        <v>907.7107505683687</v>
+        <v>907.7107505683691</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>980.951856605423</v>
+        <v>980.9518566054237</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>1.000000000004931</v>
@@ -52048,22 +52048,22 @@
         <v>0.9999999999883411</v>
       </c>
       <c r="CK264" s="397" t="n">
-        <v>0.9999999999917998</v>
+        <v>0.9999999999917996</v>
       </c>
       <c r="CL264" s="397" t="n">
         <v>0.9999999999891002</v>
       </c>
       <c r="CM264" s="398" t="n">
-        <v>0.9999999999976237</v>
+        <v>0.999999999997624</v>
       </c>
       <c r="CN264" s="102" t="n">
-        <v>0.9999873853678012</v>
+        <v>0.9999873853678002</v>
       </c>
       <c r="CO264" s="103" t="n">
         <v>1.000000000006278</v>
       </c>
       <c r="CP264" s="103" t="n">
-        <v>0.9999999999995007</v>
+        <v>0.9999999999995011</v>
       </c>
       <c r="CQ264" s="103" t="n">
         <v>1.000000000000478</v>
@@ -52078,28 +52078,28 @@
         <v>0.9999999999883411</v>
       </c>
       <c r="CV264" s="397" t="n">
-        <v>0.9999999999917998</v>
+        <v>0.9999999999917996</v>
       </c>
       <c r="CW264" s="397" t="n">
         <v>0.9999999999891002</v>
       </c>
       <c r="CX264" s="398" t="n">
-        <v>0.9999999999976237</v>
+        <v>0.999999999997624</v>
       </c>
       <c r="CY264" s="102" t="n">
-        <v>1.000000000001444</v>
+        <v>1.000000000001443</v>
       </c>
       <c r="CZ264" s="103" t="n">
         <v>1.00000000000242</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>0.9999999999934647</v>
+        <v>0.9999999999934648</v>
       </c>
       <c r="DB264" s="103" t="n">
         <v>0.999999999995553</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>0.9999999999994756</v>
+        <v>0.9999999999994754</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52120,13 +52120,13 @@
         <v>51470.9072385519</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>45635.36296202311</v>
+        <v>45635.3629620231</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>48298.6696580406</v>
+        <v>48298.66965804058</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>48006.25177548524</v>
+        <v>48006.25177548522</v>
       </c>
       <c r="DO264" s="392" t="n">
         <v>47632.4859833645</v>
@@ -52218,25 +52218,25 @@
         <v>195568.7596927182</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>214940.2738774986</v>
+        <v>214940.2738774985</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>235525.5846029741</v>
+        <v>235525.5846029742</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>2114.76287386404</v>
+        <v>2114.762873864039</v>
       </c>
       <c r="AQ265" s="372" t="n">
         <v>2255.258824119946</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>2385.81641506527</v>
+        <v>2385.816415065268</v>
       </c>
       <c r="AS265" s="372" t="n">
         <v>2524.547640124859</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>2679.06558859051</v>
+        <v>2679.065588590512</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52253,25 +52253,25 @@
         <v>195568.7596927182</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>214940.2738774986</v>
+        <v>214940.2738774985</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>235525.5846029741</v>
+        <v>235525.5846029742</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>2114.76287386404</v>
+        <v>2114.762873864039</v>
       </c>
       <c r="BH265" s="372" t="n">
         <v>2255.258824119946</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>2385.81641506527</v>
+        <v>2385.816415065268</v>
       </c>
       <c r="BJ265" s="372" t="n">
         <v>2524.547640124859</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>2679.06558859051</v>
+        <v>2679.065588590512</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,34 +52279,34 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>172806.1060695506</v>
+        <v>172806.1060695505</v>
       </c>
       <c r="BT265" s="375" t="n">
         <v>180295.7887207969</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>196800.5059366165</v>
+        <v>196800.5059366164</v>
       </c>
       <c r="BV265" s="375" t="n">
         <v>216739.6677239698</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>238022.8751124912</v>
+        <v>238022.8751124913</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>2114.76287386404</v>
+        <v>2114.762873864039</v>
       </c>
       <c r="BY265" s="372" t="n">
         <v>2255.258824119946</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>2385.81641506527</v>
+        <v>2385.816415065268</v>
       </c>
       <c r="CA265" s="372" t="n">
         <v>2524.547640124859</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>2679.06558859051</v>
+        <v>2679.065588590512</v>
       </c>
       <c r="CI265" s="396" t="n">
         <v>1.000000000036132</v>
@@ -52324,7 +52324,7 @@
         <v>0.9999999999879453</v>
       </c>
       <c r="CN265" s="102" t="n">
-        <v>0.9999791689592885</v>
+        <v>0.9999791689592887</v>
       </c>
       <c r="CO265" s="103" t="n">
         <v>0.9999999999962768</v>
@@ -52333,10 +52333,10 @@
         <v>1.000000000004635</v>
       </c>
       <c r="CQ265" s="103" t="n">
-        <v>0.9999999999975462</v>
+        <v>0.9999999999975464</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.9999999999884861</v>
+        <v>0.9999999999884857</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>1.000000000036132</v>
@@ -52354,7 +52354,7 @@
         <v>0.9999999999879453</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.000000000004147</v>
+        <v>1.000000000004148</v>
       </c>
       <c r="CZ265" s="103" t="n">
         <v>0.9999999999956886</v>
@@ -52363,10 +52363,10 @@
         <v>1.000000000004899</v>
       </c>
       <c r="DB265" s="103" t="n">
-        <v>0.9999999999979657</v>
+        <v>0.999999999997966</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>0.999999999988558</v>
+        <v>0.9999999999885576</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,7 +52384,7 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>41067.18882522403</v>
+        <v>41067.18882522402</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>36821.37305297975</v>
@@ -52396,7 +52396,7 @@
         <v>47557.42876343562</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>52673.28590222183</v>
+        <v>52673.28590222182</v>
       </c>
     </row>
     <row r="266">
@@ -52476,7 +52476,7 @@
         </is>
       </c>
       <c r="AK266" s="506" t="n">
-        <v>157813.7661646546</v>
+        <v>157813.7661646547</v>
       </c>
       <c r="AL266" s="368" t="n">
         <v>174261.8891516261</v>
@@ -52485,22 +52485,22 @@
         <v>197065.9005779591</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>220633.9572179477</v>
+        <v>220633.9572179478</v>
       </c>
       <c r="AO266" s="380" t="n">
-        <v>248391.8019773486</v>
+        <v>248391.8019773487</v>
       </c>
       <c r="AP266" s="381" t="n">
-        <v>2065.91975997967</v>
+        <v>2065.919759979672</v>
       </c>
       <c r="AQ266" s="372" t="n">
-        <v>2200.368366646069</v>
+        <v>2200.36836664607</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2410.01362293644</v>
+        <v>2410.013622936438</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2756.207409655987</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="AT266" s="382" t="n">
         <v>2961.659664538561</v>
@@ -52511,7 +52511,7 @@
         </is>
       </c>
       <c r="BB266" s="391" t="n">
-        <v>157813.7661646546</v>
+        <v>157813.7661646547</v>
       </c>
       <c r="BC266" s="375" t="n">
         <v>174261.8891516261</v>
@@ -52520,22 +52520,22 @@
         <v>197065.9005779591</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>220633.9572179477</v>
+        <v>220633.9572179478</v>
       </c>
       <c r="BF266" s="392" t="n">
-        <v>248391.8019773486</v>
+        <v>248391.8019773487</v>
       </c>
       <c r="BG266" s="386" t="n">
-        <v>2065.91975997967</v>
+        <v>2065.919759979672</v>
       </c>
       <c r="BH266" s="372" t="n">
-        <v>2200.368366646069</v>
+        <v>2200.36836664607</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2410.01362293644</v>
+        <v>2410.013622936438</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2756.207409655987</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="BK266" s="387" t="n">
         <v>2961.659664538561</v>
@@ -52555,22 +52555,22 @@
         <v>198099.827282697</v>
       </c>
       <c r="BV266" s="375" t="n">
-        <v>222315.7395968188</v>
+        <v>222315.7395968189</v>
       </c>
       <c r="BW266" s="392" t="n">
         <v>250874.0988206002</v>
       </c>
       <c r="BX266" s="386" t="n">
-        <v>2065.91975997967</v>
+        <v>2065.919759979672</v>
       </c>
       <c r="BY266" s="372" t="n">
-        <v>2200.368366646069</v>
+        <v>2200.36836664607</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2410.01362293644</v>
+        <v>2410.013622936438</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2756.207409655987</v>
+        <v>2756.207409655985</v>
       </c>
       <c r="CB266" s="387" t="n">
         <v>2961.659664538561</v>
@@ -52591,7 +52591,7 @@
         <v>1.00000000001521</v>
       </c>
       <c r="CN266" s="102" t="n">
-        <v>0.9999911678934664</v>
+        <v>0.9999911678934661</v>
       </c>
       <c r="CO266" s="103" t="n">
         <v>1.000000000002248</v>
@@ -52603,7 +52603,7 @@
         <v>1.000000000006829</v>
       </c>
       <c r="CR266" s="104" t="n">
-        <v>1.000000000003928</v>
+        <v>1.000000000003927</v>
       </c>
       <c r="CT266" s="396" t="n">
         <v>1.000000000017503</v>
@@ -52624,13 +52624,13 @@
         <v>1.000000000002145</v>
       </c>
       <c r="CZ266" s="103" t="n">
-        <v>1.000000000001179</v>
+        <v>1.00000000000118</v>
       </c>
       <c r="DA266" s="103" t="n">
         <v>1.000000000000363</v>
       </c>
       <c r="DB266" s="103" t="n">
-        <v>1.000000000006323</v>
+        <v>1.000000000006322</v>
       </c>
       <c r="DC266" s="104" t="n">
         <v>1.000000000003522</v>
@@ -52746,31 +52746,31 @@
         <v>56453.6925031906</v>
       </c>
       <c r="AL267" s="408" t="n">
-        <v>5802.278701392584</v>
+        <v>5802.278701392701</v>
       </c>
       <c r="AM267" s="408" t="n">
         <v>6277.540448684362</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>6725.091417432879</v>
+        <v>6725.091417432937</v>
       </c>
       <c r="AO267" s="409" t="n">
         <v>7204.550084947259</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>18785.44383888469</v>
+        <v>18785.44383888467</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>2605.258214999978</v>
+        <v>2605.258215000035</v>
       </c>
       <c r="AR267" s="411" t="n">
         <v>2735.52112575</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>2872.297182037506</v>
+        <v>2872.297182037526</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>3015.912041139347</v>
+        <v>3015.912041139351</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52781,31 +52781,31 @@
         <v>56453.6925031906</v>
       </c>
       <c r="BC267" s="420" t="n">
-        <v>5802.278701392584</v>
+        <v>5802.278701392701</v>
       </c>
       <c r="BD267" s="420" t="n">
         <v>6277.540448684362</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>6725.091417432879</v>
+        <v>6725.091417432937</v>
       </c>
       <c r="BF267" s="421" t="n">
         <v>7204.550084947259</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>18785.44383888469</v>
+        <v>18785.44383888467</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>2605.258214999978</v>
+        <v>2605.258215000035</v>
       </c>
       <c r="BI267" s="417" t="n">
         <v>2735.52112575</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>2872.297182037506</v>
+        <v>2872.297182037526</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>3015.912041139347</v>
+        <v>3015.912041139351</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52816,31 +52816,31 @@
         <v>56336.58064497267</v>
       </c>
       <c r="BT267" s="420" t="n">
-        <v>5785.615091863502</v>
+        <v>5785.615091863619</v>
       </c>
       <c r="BU267" s="420" t="n">
         <v>6259.511931230558</v>
       </c>
       <c r="BV267" s="420" t="n">
-        <v>6705.777574855724</v>
+        <v>6705.777574855782</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>7183.859281277408</v>
+        <v>7183.85928127741</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>18785.44383888469</v>
+        <v>18785.44383888467</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>2605.258214999978</v>
+        <v>2605.258215000035</v>
       </c>
       <c r="BZ267" s="417" t="n">
         <v>2735.52112575</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>2872.297182037506</v>
+        <v>2872.297182037526</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>3015.912041139347</v>
+        <v>3015.912041139351</v>
       </c>
       <c r="CI267" s="422" t="n">
         <v>1</v>
@@ -52861,19 +52861,19 @@
         <v>1.000000000142769</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>1.000000000572719</v>
+        <v>1.000000000572699</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>0.9999999996296435</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>0.9999999994772057</v>
+        <v>0.999999999477197</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>0.9999999997398249</v>
+        <v>0.999999999739825</v>
       </c>
       <c r="CT267" s="422" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CU267" s="423" t="n">
         <v>1</v>
@@ -52897,7 +52897,7 @@
         <v>1.000000000000557</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>0.999999999999176</v>
+        <v>0.9999999999991758</v>
       </c>
       <c r="DC267" s="134" t="n">
         <v>1.000000000000095</v>
@@ -52918,19 +52918,19 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>4417.155833637554</v>
+        <v>4417.155833637553</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>4764.761531629004</v>
+        <v>4764.761531629003</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>5167.082612404439</v>
+        <v>5167.082612404438</v>
       </c>
       <c r="DN267" s="420" t="n">
         <v>5549.162946288739</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>5955.299443328723</v>
+        <v>5955.299443328722</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -52967,7 +52967,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="L268" s="428" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="S268" s="143" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>1867.657921766596</v>
       </c>
       <c r="AC268" s="434" t="n">
-        <v>2039.437784453357</v>
+        <v>2039.437784453358</v>
       </c>
       <c r="AJ268" s="150" t="inlineStr">
         <is>
@@ -53010,22 +53010,22 @@
         </is>
       </c>
       <c r="AK268" s="435" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400754</v>
       </c>
       <c r="AL268" s="408" t="n">
         <v>470981.9918168656</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>514533.4454606617</v>
+        <v>514533.4454606615</v>
       </c>
       <c r="AN268" s="408" t="n">
         <v>560230.254048805</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>611485.4023741342</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>1595.934018942288</v>
+        <v>1595.934018942289</v>
       </c>
       <c r="AQ268" s="437" t="n">
         <v>1569.022329063146</v>
@@ -53037,7 +53037,7 @@
         <v>1883.427091547451</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>2059.761192982157</v>
+        <v>2059.761192982159</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53045,22 +53045,22 @@
         </is>
       </c>
       <c r="BB268" s="439" t="n">
-        <v>500699.1934400753</v>
+        <v>500699.1934400754</v>
       </c>
       <c r="BC268" s="440" t="n">
         <v>470981.9918168656</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>514533.4454606617</v>
+        <v>514533.4454606615</v>
       </c>
       <c r="BE268" s="440" t="n">
         <v>560230.254048805</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>611485.4023741342</v>
+        <v>611485.4023741344</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>1595.934018942288</v>
+        <v>1595.934018942289</v>
       </c>
       <c r="BH268" s="443" t="n">
         <v>1569.022329063146</v>
@@ -53072,7 +53072,7 @@
         <v>1883.427091547451</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>2059.761192982157</v>
+        <v>2059.761192982159</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53080,25 +53080,25 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>500845.7947322577</v>
+        <v>500845.7947322578</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>472219.6385785875</v>
+        <v>472219.6385785876</v>
       </c>
       <c r="BU268" s="440" t="n">
-        <v>517101.5044096496</v>
+        <v>517101.5044096495</v>
       </c>
       <c r="BV268" s="440" t="n">
         <v>564300.9875857062</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>617393.3372501315</v>
+        <v>617393.3372501316</v>
       </c>
       <c r="BX268" s="442" t="n">
         <v>1596.752449216725</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>1570.164229810026</v>
+        <v>1570.164229810027</v>
       </c>
       <c r="BZ268" s="443" t="n">
         <v>1707.664593191014</v>
@@ -53107,7 +53107,7 @@
         <v>1884.523741338131</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>2060.705553828572</v>
+        <v>2060.705553828574</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53128,10 +53128,10 @@
         <v>183894.2944744075</v>
       </c>
       <c r="DL268" s="440" t="n">
-        <v>185270.0027580661</v>
+        <v>185270.002758066</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>213060.0023781853</v>
+        <v>213060.0023781852</v>
       </c>
       <c r="DN268" s="440" t="n">
         <v>244491.9258501469</v>
@@ -54059,31 +54059,31 @@
         <v>0</v>
       </c>
       <c r="AP276" s="194" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="AQ276" s="179" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AR276" s="179" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="AS276" s="179" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="AT276" s="195" t="n">
         <v>32.09902961138318</v>
       </c>
       <c r="AU276" s="190" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="AV276" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW276" s="190" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="AX276" s="190" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="AY276" s="196" t="n">
         <v>32.09902961138318</v>
@@ -54109,31 +54109,31 @@
         <v>0</v>
       </c>
       <c r="BG276" s="197" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="BH276" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BI276" s="190" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="BJ276" s="190" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="BK276" s="198" t="n">
         <v>32.09902961138318</v>
       </c>
       <c r="BL276" s="199" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="BM276" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN276" s="200" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="BO276" s="200" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="BP276" s="201" t="n">
         <v>32.09902961138318</v>
@@ -54159,10 +54159,10 @@
         <v>0</v>
       </c>
       <c r="BX276" s="197" t="n">
-        <v>95.97568964536505</v>
+        <v>95.97568964536502</v>
       </c>
       <c r="BY276" s="190" t="n">
-        <v>75.09334929877637</v>
+        <v>75.09334929877639</v>
       </c>
       <c r="BZ276" s="190" t="n">
         <v>39.62531155453664</v>
@@ -54174,10 +54174,10 @@
         <v>32.63877585077145</v>
       </c>
       <c r="CC276" s="199" t="n">
-        <v>95.97568964536505</v>
+        <v>95.97568964536502</v>
       </c>
       <c r="CD276" s="200" t="n">
-        <v>75.09334929877637</v>
+        <v>75.09334929877639</v>
       </c>
       <c r="CE276" s="200" t="n">
         <v>39.62531155453664</v>
@@ -54339,31 +54339,31 @@
         <v>0</v>
       </c>
       <c r="AP277" s="194" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="AQ277" s="179" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="AR277" s="179" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="AS277" s="179" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="AT277" s="195" t="n">
         <v>30.53249016319823</v>
       </c>
       <c r="AU277" s="190" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="AV277" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="AW277" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="AX277" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="AY277" s="196" t="n">
         <v>30.53249016319823</v>
@@ -54389,31 +54389,31 @@
         <v>0</v>
       </c>
       <c r="BG277" s="197" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="BH277" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="BI277" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="BJ277" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="BK277" s="198" t="n">
         <v>30.53249016319823</v>
       </c>
       <c r="BL277" s="197" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="BM277" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="BN277" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="BO277" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="BP277" s="198" t="n">
         <v>30.53249016319823</v>
@@ -54439,10 +54439,10 @@
         <v>0</v>
       </c>
       <c r="BX277" s="197" t="n">
-        <v>61.55534330250131</v>
+        <v>61.5553433025013</v>
       </c>
       <c r="BY277" s="190" t="n">
-        <v>47.28054258672604</v>
+        <v>47.28054258672603</v>
       </c>
       <c r="BZ277" s="190" t="n">
         <v>33.13520019411198</v>
@@ -54454,10 +54454,10 @@
         <v>30.60683374054721</v>
       </c>
       <c r="CC277" s="197" t="n">
-        <v>61.55534330250131</v>
+        <v>61.5553433025013</v>
       </c>
       <c r="CD277" s="190" t="n">
-        <v>47.28054258672604</v>
+        <v>47.28054258672603</v>
       </c>
       <c r="CE277" s="190" t="n">
         <v>33.13520019411198</v>
@@ -54884,13 +54884,13 @@
         </is>
       </c>
       <c r="AK279" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL279" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM279" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN279" s="207" t="n">
         <v>17.11580126467504</v>
@@ -54899,10 +54899,10 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP279" s="206" t="n">
-        <v>27.83815954640791</v>
+        <v>27.83815954640792</v>
       </c>
       <c r="AQ279" s="207" t="n">
-        <v>28.00612562612424</v>
+        <v>28.00612562612425</v>
       </c>
       <c r="AR279" s="207" t="n">
         <v>22.54630249853268</v>
@@ -54917,10 +54917,10 @@
         <v>33.28550242320334</v>
       </c>
       <c r="AV279" s="209" t="n">
-        <v>35.02138415499929</v>
+        <v>35.0213841549993</v>
       </c>
       <c r="AW279" s="209" t="n">
-        <v>36.13869245874403</v>
+        <v>36.13869245874402</v>
       </c>
       <c r="AX279" s="209" t="n">
         <v>37.10430664523566</v>
@@ -54934,13 +54934,13 @@
         </is>
       </c>
       <c r="BB279" s="211" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC279" s="212" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD279" s="212" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE279" s="212" t="n">
         <v>17.11580126467504</v>
@@ -54949,10 +54949,10 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG279" s="211" t="n">
-        <v>27.83815954640791</v>
+        <v>27.83815954640792</v>
       </c>
       <c r="BH279" s="212" t="n">
-        <v>28.00612562612424</v>
+        <v>28.00612562612425</v>
       </c>
       <c r="BI279" s="212" t="n">
         <v>22.54630249853268</v>
@@ -54967,10 +54967,10 @@
         <v>33.28550242320334</v>
       </c>
       <c r="BM279" s="212" t="n">
-        <v>35.02138415499929</v>
+        <v>35.0213841549993</v>
       </c>
       <c r="BN279" s="212" t="n">
-        <v>36.13869245874403</v>
+        <v>36.13869245874402</v>
       </c>
       <c r="BO279" s="212" t="n">
         <v>37.10430664523566</v>
@@ -54984,7 +54984,7 @@
         </is>
       </c>
       <c r="BS279" s="211" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BT279" s="212" t="n">
         <v>6.91019437641005</v>
@@ -55002,7 +55002,7 @@
         <v>27.91096473231612</v>
       </c>
       <c r="BY279" s="212" t="n">
-        <v>28.11758592367503</v>
+        <v>28.11758592367504</v>
       </c>
       <c r="BZ279" s="212" t="n">
         <v>22.6974477923026</v>
@@ -55014,13 +55014,13 @@
         <v>20.54199047333498</v>
       </c>
       <c r="CC279" s="212" t="n">
-        <v>33.29173660426514</v>
+        <v>33.29173660426515</v>
       </c>
       <c r="CD279" s="212" t="n">
         <v>35.02778030008508</v>
       </c>
       <c r="CE279" s="212" t="n">
-        <v>36.14528298267898</v>
+        <v>36.14528298267897</v>
       </c>
       <c r="CF279" s="212" t="n">
         <v>37.11103082499601</v>
@@ -55079,7 +55079,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H280" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I280" s="215" t="n">
         <v>258.2717129066096</v>
@@ -55088,7 +55088,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="K280" s="215" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="L280" s="216" t="n">
         <v>182.5988128429346</v>
@@ -55100,7 +55100,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="O280" s="215" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="P280" s="215" t="n">
         <v>199.9191344202025</v>
@@ -55129,7 +55129,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y280" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z280" s="218" t="n">
         <v>258.2717129066096</v>
@@ -55138,7 +55138,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="AB280" s="218" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="AC280" s="219" t="n">
         <v>182.5988128429346</v>
@@ -55150,7 +55150,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="AF280" s="218" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="AG280" s="218" t="n">
         <v>199.9191344202025</v>
@@ -55164,13 +55164,13 @@
         </is>
       </c>
       <c r="AK280" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL280" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM280" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN280" s="207" t="n">
         <v>17.11580126467504</v>
@@ -55179,7 +55179,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP280" s="206" t="n">
-        <v>301.0218825085428</v>
+        <v>301.0218825085427</v>
       </c>
       <c r="AQ280" s="207" t="n">
         <v>259.972299350457</v>
@@ -55188,7 +55188,7 @@
         <v>195.9572318509364</v>
       </c>
       <c r="AS280" s="207" t="n">
-        <v>184.5460315779279</v>
+        <v>184.5460315779278</v>
       </c>
       <c r="AT280" s="208" t="n">
         <v>184.1393065227</v>
@@ -55197,7 +55197,7 @@
         <v>306.4692253853382</v>
       </c>
       <c r="AV280" s="207" t="n">
-        <v>266.987557879332</v>
+        <v>266.9875578793321</v>
       </c>
       <c r="AW280" s="207" t="n">
         <v>209.5496218111478</v>
@@ -55214,13 +55214,13 @@
         </is>
       </c>
       <c r="BB280" s="221" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC280" s="222" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD280" s="222" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE280" s="222" t="n">
         <v>17.11580126467504</v>
@@ -55229,7 +55229,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG280" s="221" t="n">
-        <v>301.0218825085428</v>
+        <v>301.0218825085427</v>
       </c>
       <c r="BH280" s="222" t="n">
         <v>259.972299350457</v>
@@ -55238,7 +55238,7 @@
         <v>195.9572318509364</v>
       </c>
       <c r="BJ280" s="222" t="n">
-        <v>184.5460315779279</v>
+        <v>184.5460315779278</v>
       </c>
       <c r="BK280" s="214" t="n">
         <v>184.1393065227</v>
@@ -55247,7 +55247,7 @@
         <v>306.4692253853382</v>
       </c>
       <c r="BM280" s="222" t="n">
-        <v>266.987557879332</v>
+        <v>266.9875578793321</v>
       </c>
       <c r="BN280" s="222" t="n">
         <v>209.5496218111478</v>
@@ -55264,7 +55264,7 @@
         </is>
       </c>
       <c r="BS280" s="221" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BT280" s="222" t="n">
         <v>6.91019437641005</v>
@@ -58306,31 +58306,31 @@
         <v>0</v>
       </c>
       <c r="AP294" s="194" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="AQ294" s="179" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AR294" s="179" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="AS294" s="179" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="AT294" s="195" t="n">
         <v>32.09902961138318</v>
       </c>
       <c r="AU294" s="190" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="AV294" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW294" s="190" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="AX294" s="190" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="AY294" s="196" t="n">
         <v>32.09902961138318</v>
@@ -58356,31 +58356,31 @@
         <v>0</v>
       </c>
       <c r="BG294" s="197" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="BH294" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BI294" s="190" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="BJ294" s="190" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="BK294" s="198" t="n">
         <v>32.09902961138318</v>
       </c>
       <c r="BL294" s="199" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="BM294" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN294" s="200" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="BO294" s="200" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="BP294" s="201" t="n">
         <v>32.09902961138318</v>
@@ -58406,10 +58406,10 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>95.97568964536505</v>
+        <v>95.97568964536502</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>75.09334929877636</v>
+        <v>75.09334929877637</v>
       </c>
       <c r="BZ294" s="190" t="n">
         <v>39.62531155453664</v>
@@ -58421,10 +58421,10 @@
         <v>32.63877585077145</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>95.97568964536505</v>
+        <v>95.97568964536502</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>75.09334929877636</v>
+        <v>75.09334929877637</v>
       </c>
       <c r="CE294" s="200" t="n">
         <v>39.62531155453664</v>
@@ -58463,13 +58463,13 @@
         <v>2844</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>0.6305845188212781</v>
+        <v>0.630584518821278</v>
       </c>
       <c r="CX294" s="200" t="n">
         <v>0.558827441437645</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5575524490099094</v>
+        <v>0.5575524490099095</v>
       </c>
       <c r="CZ294" s="200" t="n">
         <v>0.5519744899569327</v>
@@ -58601,31 +58601,31 @@
         <v>0</v>
       </c>
       <c r="AP295" s="194" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="AQ295" s="179" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="AR295" s="179" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="AS295" s="179" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="AT295" s="195" t="n">
         <v>30.53249016319823</v>
       </c>
       <c r="AU295" s="190" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="AV295" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="AW295" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="AX295" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="AY295" s="196" t="n">
         <v>30.53249016319823</v>
@@ -58651,31 +58651,31 @@
         <v>0</v>
       </c>
       <c r="BG295" s="197" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="BH295" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="BI295" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="BJ295" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="BK295" s="198" t="n">
         <v>30.53249016319823</v>
       </c>
       <c r="BL295" s="197" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="BM295" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="BN295" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="BO295" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="BP295" s="198" t="n">
         <v>30.53249016319823</v>
@@ -58701,10 +58701,10 @@
         <v>0</v>
       </c>
       <c r="BX295" s="197" t="n">
-        <v>61.55534330250131</v>
+        <v>61.55534330250129</v>
       </c>
       <c r="BY295" s="190" t="n">
-        <v>47.28054258672604</v>
+        <v>47.28054258672603</v>
       </c>
       <c r="BZ295" s="190" t="n">
         <v>33.13520019411198</v>
@@ -58716,10 +58716,10 @@
         <v>30.60683374054721</v>
       </c>
       <c r="CC295" s="197" t="n">
-        <v>61.55534330250131</v>
+        <v>61.55534330250129</v>
       </c>
       <c r="CD295" s="190" t="n">
-        <v>47.28054258672604</v>
+        <v>47.28054258672603</v>
       </c>
       <c r="CE295" s="190" t="n">
         <v>33.13520019411198</v>
@@ -58764,7 +58764,7 @@
         <v>0.08086620964934653</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>0.08294050297335381</v>
+        <v>0.0829405029733538</v>
       </c>
       <c r="CZ295" s="190" t="n">
         <v>0.08529935814312077</v>
@@ -59053,7 +59053,7 @@
         <v>10888</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>0.07538747908594198</v>
+        <v>0.07538747908594197</v>
       </c>
       <c r="CX296" s="190" t="n">
         <v>0.07577105569712549</v>
@@ -59062,7 +59062,7 @@
         <v>0.0753392708449033</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>0.07539709805810331</v>
+        <v>0.07539709805810332</v>
       </c>
       <c r="DA296" s="198" t="n">
         <v>0.07495273739913609</v>
@@ -59176,13 +59176,13 @@
         </is>
       </c>
       <c r="AK297" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL297" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM297" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN297" s="207" t="n">
         <v>17.11580126467504</v>
@@ -59191,10 +59191,10 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP297" s="206" t="n">
-        <v>27.83815954640791</v>
+        <v>27.83815954640792</v>
       </c>
       <c r="AQ297" s="207" t="n">
-        <v>28.00612562612424</v>
+        <v>28.00612562612425</v>
       </c>
       <c r="AR297" s="207" t="n">
         <v>22.54630249853268</v>
@@ -59209,10 +59209,10 @@
         <v>33.28550242320334</v>
       </c>
       <c r="AV297" s="209" t="n">
-        <v>35.02138415499929</v>
+        <v>35.0213841549993</v>
       </c>
       <c r="AW297" s="209" t="n">
-        <v>36.13869245874403</v>
+        <v>36.13869245874402</v>
       </c>
       <c r="AX297" s="209" t="n">
         <v>37.10430664523566</v>
@@ -59226,13 +59226,13 @@
         </is>
       </c>
       <c r="BB297" s="211" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC297" s="212" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD297" s="212" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE297" s="212" t="n">
         <v>17.11580126467504</v>
@@ -59241,10 +59241,10 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG297" s="211" t="n">
-        <v>27.83815954640791</v>
+        <v>27.83815954640792</v>
       </c>
       <c r="BH297" s="212" t="n">
-        <v>28.00612562612424</v>
+        <v>28.00612562612425</v>
       </c>
       <c r="BI297" s="212" t="n">
         <v>22.54630249853268</v>
@@ -59259,10 +59259,10 @@
         <v>33.28550242320334</v>
       </c>
       <c r="BM297" s="212" t="n">
-        <v>35.02138415499929</v>
+        <v>35.0213841549993</v>
       </c>
       <c r="BN297" s="212" t="n">
-        <v>36.13869245874403</v>
+        <v>36.13869245874402</v>
       </c>
       <c r="BO297" s="212" t="n">
         <v>37.10430664523566</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="BS297" s="211" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BT297" s="212" t="n">
         <v>6.91019437641005</v>
@@ -59294,7 +59294,7 @@
         <v>27.91096473231612</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>28.11758592367503</v>
+        <v>28.11758592367504</v>
       </c>
       <c r="BZ297" s="212" t="n">
         <v>22.6974477923026</v>
@@ -59306,13 +59306,13 @@
         <v>20.54199047333497</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>33.29173660426514</v>
+        <v>33.29173660426515</v>
       </c>
       <c r="CD297" s="212" t="n">
         <v>35.02778030008508</v>
       </c>
       <c r="CE297" s="212" t="n">
-        <v>36.14528298267898</v>
+        <v>36.14528298267897</v>
       </c>
       <c r="CF297" s="212" t="n">
         <v>37.11103082499601</v>
@@ -59348,19 +59348,19 @@
         <v>2178</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.006234181061802671</v>
+        <v>0.006234181061802452</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.006396145085788304</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945178</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.006724179760346101</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885683</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59386,7 +59386,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="H298" s="215" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="I298" s="215" t="n">
         <v>258.2717129066096</v>
@@ -59395,7 +59395,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="K298" s="215" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="L298" s="216" t="n">
         <v>182.5988128429346</v>
@@ -59407,7 +59407,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="O298" s="215" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="P298" s="215" t="n">
         <v>199.9191344202025</v>
@@ -59436,7 +59436,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="Y298" s="217" t="n">
-        <v>299.758612470945</v>
+        <v>299.7586124709451</v>
       </c>
       <c r="Z298" s="218" t="n">
         <v>258.2717129066096</v>
@@ -59445,7 +59445,7 @@
         <v>194.2372157444536</v>
       </c>
       <c r="AB298" s="218" t="n">
-        <v>182.8033331555275</v>
+        <v>182.8033331555274</v>
       </c>
       <c r="AC298" s="219" t="n">
         <v>182.5988128429346</v>
@@ -59457,7 +59457,7 @@
         <v>265.2869714354846</v>
       </c>
       <c r="AF298" s="218" t="n">
-        <v>207.829605704665</v>
+        <v>207.8296057046649</v>
       </c>
       <c r="AG298" s="218" t="n">
         <v>199.9191344202025</v>
@@ -59471,13 +59471,13 @@
         </is>
       </c>
       <c r="AK298" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL298" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM298" s="207" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="AN298" s="207" t="n">
         <v>17.11580126467504</v>
@@ -59486,7 +59486,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="AP298" s="206" t="n">
-        <v>301.0218825085428</v>
+        <v>301.0218825085427</v>
       </c>
       <c r="AQ298" s="207" t="n">
         <v>259.972299350457</v>
@@ -59495,7 +59495,7 @@
         <v>195.9572318509364</v>
       </c>
       <c r="AS298" s="207" t="n">
-        <v>184.5460315779279</v>
+        <v>184.5460315779278</v>
       </c>
       <c r="AT298" s="208" t="n">
         <v>184.1393065227</v>
@@ -59504,7 +59504,7 @@
         <v>306.4692253853382</v>
       </c>
       <c r="AV298" s="207" t="n">
-        <v>266.987557879332</v>
+        <v>266.9875578793321</v>
       </c>
       <c r="AW298" s="207" t="n">
         <v>209.5496218111478</v>
@@ -59521,13 +59521,13 @@
         </is>
       </c>
       <c r="BB298" s="221" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC298" s="222" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD298" s="222" t="n">
-        <v>13.59238996021135</v>
+        <v>13.59238996021134</v>
       </c>
       <c r="BE298" s="222" t="n">
         <v>17.11580126467504</v>
@@ -59536,7 +59536,7 @@
         <v>17.86531224755395</v>
       </c>
       <c r="BG298" s="221" t="n">
-        <v>301.0218825085428</v>
+        <v>301.0218825085427</v>
       </c>
       <c r="BH298" s="222" t="n">
         <v>259.972299350457</v>
@@ -59545,7 +59545,7 @@
         <v>195.9572318509364</v>
       </c>
       <c r="BJ298" s="222" t="n">
-        <v>184.5460315779279</v>
+        <v>184.5460315779278</v>
       </c>
       <c r="BK298" s="214" t="n">
         <v>184.1393065227</v>
@@ -59554,7 +59554,7 @@
         <v>306.4692253853382</v>
       </c>
       <c r="BM298" s="222" t="n">
-        <v>266.987557879332</v>
+        <v>266.9875578793321</v>
       </c>
       <c r="BN298" s="222" t="n">
         <v>209.5496218111478</v>
@@ -59571,7 +59571,7 @@
         </is>
       </c>
       <c r="BS298" s="221" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BT298" s="222" t="n">
         <v>6.91019437641005</v>
@@ -59643,19 +59643,19 @@
         <v>22276</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>0.8093751493808196</v>
+        <v>0.8093751493808192</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7218608518699053</v>
+        <v>0.721860851869905</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.7224227467631119</v>
+        <v>0.7224227467631118</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.7193951259185029</v>
+        <v>0.7193951259185026</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.6959031002622666</v>
+        <v>0.6959031002622664</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60437,16 +60437,16 @@
         <v>0</v>
       </c>
       <c r="AU303" s="190" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="AV303" s="190" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="AW303" s="190" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="AX303" s="190" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="AY303" s="196" t="n">
         <v>32.09902961138318</v>
@@ -60487,16 +60487,16 @@
         <v>0</v>
       </c>
       <c r="BL303" s="199" t="n">
-        <v>95.34510512654377</v>
+        <v>95.34510512654374</v>
       </c>
       <c r="BM303" s="200" t="n">
-        <v>74.53452185733872</v>
+        <v>74.53452185733873</v>
       </c>
       <c r="BN303" s="200" t="n">
         <v>39.06775910552673</v>
       </c>
       <c r="BO303" s="200" t="n">
-        <v>32.56809833624369</v>
+        <v>32.5680983362437</v>
       </c>
       <c r="BP303" s="201" t="n">
         <v>32.09902961138318</v>
@@ -60522,7 +60522,7 @@
         <v>0</v>
       </c>
       <c r="BX303" s="462" t="n">
-        <v>0.08725993081426574</v>
+        <v>0.08725993081426577</v>
       </c>
       <c r="BY303" s="463" t="n">
         <v>-0.007554203388694719</v>
@@ -60531,7 +60531,7 @@
         <v>-0.01447804354785405</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>-0.01724051582905627</v>
+        <v>-0.01724051582905626</v>
       </c>
       <c r="CB303" s="464" t="n">
         <v>-0.01710261392903577</v>
@@ -60543,7 +60543,7 @@
         <v>-0.5672704337412526</v>
       </c>
       <c r="CE303" s="200" t="n">
-        <v>-0.5736969862838657</v>
+        <v>-0.5736969862838659</v>
       </c>
       <c r="CF303" s="200" t="n">
         <v>-0.5710071398196082</v>
@@ -60689,16 +60689,16 @@
         <v>0</v>
       </c>
       <c r="AU304" s="190" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="AV304" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="AW304" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="AX304" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="AY304" s="196" t="n">
         <v>30.53249016319823</v>
@@ -60739,16 +60739,16 @@
         <v>0</v>
       </c>
       <c r="BL304" s="197" t="n">
-        <v>61.45817433208951</v>
+        <v>61.4581743320895</v>
       </c>
       <c r="BM304" s="190" t="n">
-        <v>47.19967637707669</v>
+        <v>47.19967637707668</v>
       </c>
       <c r="BN304" s="190" t="n">
         <v>33.05225969113863</v>
       </c>
       <c r="BO304" s="190" t="n">
-        <v>30.32862845497404</v>
+        <v>30.32862845497403</v>
       </c>
       <c r="BP304" s="198" t="n">
         <v>30.53249016319823</v>
@@ -60774,7 +60774,7 @@
         <v>0</v>
       </c>
       <c r="BX304" s="462" t="n">
-        <v>0.08665162380508083</v>
+        <v>0.08665162380508086</v>
       </c>
       <c r="BY304" s="463" t="n">
         <v>-0.001716219262795569</v>
@@ -60789,13 +60789,13 @@
         <v>-0.002440843770300764</v>
       </c>
       <c r="CC304" s="197" t="n">
-        <v>5.333870451040945</v>
+        <v>5.333870451040946</v>
       </c>
       <c r="CD304" s="190" t="n">
         <v>-0.08114377794276546</v>
       </c>
       <c r="CE304" s="190" t="n">
-        <v>-0.08335780774050484</v>
+        <v>-0.08335780774050483</v>
       </c>
       <c r="CF304" s="190" t="n">
         <v>-0.08578052081382628</v>
@@ -61196,7 +61196,7 @@
         <v>27.90473055125432</v>
       </c>
       <c r="AV306" s="209" t="n">
-        <v>28.11118977858924</v>
+        <v>28.11118977858925</v>
       </c>
       <c r="AW306" s="209" t="n">
         <v>22.69085726836766</v>
@@ -61246,7 +61246,7 @@
         <v>27.90473055125432</v>
       </c>
       <c r="BM306" s="212" t="n">
-        <v>28.11118977858924</v>
+        <v>28.11118977858925</v>
       </c>
       <c r="BN306" s="212" t="n">
         <v>22.69085726836766</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.0002234593929034625</v>
+        <v>-0.0002234593929034546</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0002275819979038566</v>
+        <v>-0.0002275819979038485</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0002905328177100054</v>
+        <v>-0.0002905328177099953</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0003334198850995083</v>
+        <v>-0.0003334198850994967</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0003341999268680639</v>
+        <v>-0.0003341999268680523</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.006236967234433312</v>
+        <v>-0.006236967234433093</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.006399056380743317</v>
+        <v>-0.006399056380743093</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.006594353461923418</v>
+        <v>-0.006594353461923188</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.006728663710832268</v>
+        <v>-0.006728663710832034</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.006865131713913014</v>
+        <v>-0.006865131713912774</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61445,7 +61445,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="AU307" s="207" t="n">
-        <v>301.0884535133892</v>
+        <v>301.0884535133891</v>
       </c>
       <c r="AV307" s="207" t="n">
         <v>260.077363502922</v>
@@ -61495,7 +61495,7 @@
         <v>0.2290284821556444</v>
       </c>
       <c r="BL307" s="222" t="n">
-        <v>301.0884535133892</v>
+        <v>301.0884535133891</v>
       </c>
       <c r="BM307" s="222" t="n">
         <v>260.077363502922</v>
@@ -61530,7 +61530,7 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX307" s="466" t="n">
-        <v>0.1042053931330955</v>
+        <v>0.1042053931330956</v>
       </c>
       <c r="BY307" s="467" t="n">
         <v>0.01826537562766166</v>
@@ -61542,7 +61542,7 @@
         <v>0.05408945665275691</v>
       </c>
       <c r="CB307" s="468" t="n">
-        <v>0.07761131085169017</v>
+        <v>0.07761131085169018</v>
       </c>
       <c r="CC307" s="212" t="n">
         <v>31.45938192183187</v>
@@ -63063,7 +63063,7 @@
         </is>
       </c>
       <c r="AK315" s="220" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="AL315" s="209" t="n">
         <v>6.91019437641005</v>
@@ -63078,13 +63078,13 @@
         <v>17.63628376539831</v>
       </c>
       <c r="AP315" s="489" t="n">
-        <v>0.1636551195032611</v>
+        <v>0.163655119503261</v>
       </c>
       <c r="AQ315" s="490" t="n">
-        <v>0.200313571211994</v>
+        <v>0.2003135712119939</v>
       </c>
       <c r="AR315" s="490" t="n">
-        <v>0.3761173699277701</v>
+        <v>0.3761173699277702</v>
       </c>
       <c r="AS315" s="490" t="n">
         <v>0.4612888047827939</v>
@@ -63093,10 +63093,10 @@
         <v>0.4680285721514659</v>
       </c>
       <c r="AU315" s="490" t="n">
-        <v>0.1616551195032611</v>
+        <v>0.161655119503261</v>
       </c>
       <c r="AV315" s="490" t="n">
-        <v>0.197313571211994</v>
+        <v>0.1973135712119939</v>
       </c>
       <c r="AW315" s="490" t="n">
         <v>0.3721173699277702</v>
@@ -63113,7 +63113,7 @@
         </is>
       </c>
       <c r="BB315" s="211" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BC315" s="212" t="n">
         <v>6.91019437641005</v>
@@ -63128,13 +63128,13 @@
         <v>17.63628376539831</v>
       </c>
       <c r="BG315" s="466" t="n">
-        <v>0.1636551195032611</v>
+        <v>0.163655119503261</v>
       </c>
       <c r="BH315" s="467" t="n">
-        <v>0.200313571211994</v>
+        <v>0.2003135712119939</v>
       </c>
       <c r="BI315" s="467" t="n">
-        <v>0.3761173699277701</v>
+        <v>0.3761173699277702</v>
       </c>
       <c r="BJ315" s="467" t="n">
         <v>0.4612888047827939</v>
@@ -63143,10 +63143,10 @@
         <v>0.4680285721514659</v>
       </c>
       <c r="BL315" s="467" t="n">
-        <v>0.1616551195032611</v>
+        <v>0.161655119503261</v>
       </c>
       <c r="BM315" s="467" t="n">
-        <v>0.197313571211994</v>
+        <v>0.1973135712119939</v>
       </c>
       <c r="BN315" s="467" t="n">
         <v>0.3721173699277702</v>
@@ -63178,7 +63178,7 @@
         <v>0</v>
       </c>
       <c r="BX315" s="466" t="n">
-        <v>0.161624848108995</v>
+        <v>0.1616248481089949</v>
       </c>
       <c r="BY315" s="467" t="n">
         <v>0.1972775413460403</v>
@@ -63236,28 +63236,28 @@
         <v>0.01784808841815988</v>
       </c>
       <c r="I316" s="495" t="n">
-        <v>0.02644403715310645</v>
+        <v>0.02644403715310646</v>
       </c>
       <c r="J316" s="495" t="n">
-        <v>0.06540160586902488</v>
+        <v>0.0654016058690249</v>
       </c>
       <c r="K316" s="495" t="n">
-        <v>0.0856136222994042</v>
+        <v>0.08561362229940421</v>
       </c>
       <c r="L316" s="496" t="n">
         <v>0.08911974768298138</v>
       </c>
       <c r="M316" s="495" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="N316" s="495" t="n">
         <v>0.02604799752893461</v>
       </c>
       <c r="O316" s="495" t="n">
-        <v>0.06470606122154865</v>
+        <v>0.06470606122154866</v>
       </c>
       <c r="P316" s="495" t="n">
-        <v>0.08468563942390696</v>
+        <v>0.08468563942390697</v>
       </c>
       <c r="Q316" s="496" t="n">
         <v>0.08797725656616802</v>
@@ -63286,28 +63286,28 @@
         <v>0.01784808841815988</v>
       </c>
       <c r="Z316" s="498" t="n">
-        <v>0.02644403715310645</v>
+        <v>0.02644403715310646</v>
       </c>
       <c r="AA316" s="498" t="n">
-        <v>0.06540160586902488</v>
+        <v>0.0654016058690249</v>
       </c>
       <c r="AB316" s="498" t="n">
-        <v>0.0856136222994042</v>
+        <v>0.08561362229940421</v>
       </c>
       <c r="AC316" s="499" t="n">
         <v>0.08911974768298138</v>
       </c>
       <c r="AD316" s="498" t="n">
-        <v>0.01762997011581366</v>
+        <v>0.01762997011581365</v>
       </c>
       <c r="AE316" s="498" t="n">
         <v>0.02604799752893461</v>
       </c>
       <c r="AF316" s="498" t="n">
-        <v>0.06470606122154865</v>
+        <v>0.06470606122154866</v>
       </c>
       <c r="AG316" s="498" t="n">
-        <v>0.08468563942390696</v>
+        <v>0.08468563942390697</v>
       </c>
       <c r="AH316" s="499" t="n">
         <v>0.08797725656616802</v>
@@ -63318,7 +63318,7 @@
         </is>
       </c>
       <c r="AK316" s="206" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="AL316" s="207" t="n">
         <v>6.91019437641005</v>
@@ -63339,7 +63339,7 @@
         <v>0.02627560094783769</v>
       </c>
       <c r="AR316" s="501" t="n">
-        <v>0.06486477924766289</v>
+        <v>0.06486477924766287</v>
       </c>
       <c r="AS316" s="501" t="n">
         <v>0.08487377617971927</v>
@@ -63354,7 +63354,7 @@
         <v>0.02588208391168995</v>
       </c>
       <c r="AW316" s="501" t="n">
-        <v>0.06417494373955945</v>
+        <v>0.06417494373955944</v>
       </c>
       <c r="AX316" s="501" t="n">
         <v>0.0839538126416958</v>
@@ -63368,7 +63368,7 @@
         </is>
       </c>
       <c r="BB316" s="221" t="n">
-        <v>5.380771871949022</v>
+        <v>5.380771871949021</v>
       </c>
       <c r="BC316" s="222" t="n">
         <v>6.91019437641005</v>
@@ -63389,7 +63389,7 @@
         <v>0.02627560094783769</v>
       </c>
       <c r="BI316" s="504" t="n">
-        <v>0.06486477924766289</v>
+        <v>0.06486477924766287</v>
       </c>
       <c r="BJ316" s="504" t="n">
         <v>0.08487377617971927</v>
@@ -63404,7 +63404,7 @@
         <v>0.02588208391168995</v>
       </c>
       <c r="BN316" s="504" t="n">
-        <v>0.06417494373955945</v>
+        <v>0.06417494373955944</v>
       </c>
       <c r="BO316" s="504" t="n">
         <v>0.0839538126416958</v>
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="AK326" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL326" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64727,7 +64727,7 @@
         </is>
       </c>
       <c r="BB326" s="419" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC326" s="420" t="n">
         <v>182926.8615295583</v>
@@ -64762,7 +64762,7 @@
         </is>
       </c>
       <c r="BS326" s="419" t="n">
-        <v>97546.97984266913</v>
+        <v>97546.97984266911</v>
       </c>
       <c r="BT326" s="420" t="n">
         <v>180187.2539170122</v>
@@ -64887,7 +64887,7 @@
         </is>
       </c>
       <c r="AK327" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL327" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64922,7 +64922,7 @@
         </is>
       </c>
       <c r="BB327" s="439" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC327" s="440" t="n">
         <v>182926.8615295583</v>
@@ -64957,7 +64957,7 @@
         </is>
       </c>
       <c r="BS327" s="439" t="n">
-        <v>97546.97984266913</v>
+        <v>97546.97984266911</v>
       </c>
       <c r="BT327" s="440" t="n">
         <v>180187.2539170122</v>
@@ -67590,7 +67590,7 @@
         </is>
       </c>
       <c r="AK344" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL344" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67625,7 +67625,7 @@
         </is>
       </c>
       <c r="BB344" s="419" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC344" s="420" t="n">
         <v>182926.8615295583</v>
@@ -67660,7 +67660,7 @@
         </is>
       </c>
       <c r="BS344" s="419" t="n">
-        <v>97546.97984266913</v>
+        <v>97546.97984266911</v>
       </c>
       <c r="BT344" s="420" t="n">
         <v>180187.2539170122</v>
@@ -67785,7 +67785,7 @@
         </is>
       </c>
       <c r="AK345" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL345" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
       <c r="BB345" s="439" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC345" s="440" t="n">
         <v>182926.8615295583</v>
@@ -67855,7 +67855,7 @@
         </is>
       </c>
       <c r="BS345" s="439" t="n">
-        <v>97546.97984266913</v>
+        <v>97546.97984266911</v>
       </c>
       <c r="BT345" s="440" t="n">
         <v>180187.2539170122</v>
@@ -68437,16 +68437,16 @@
         <v>15461.55643869437</v>
       </c>
       <c r="AP350" s="381" t="n">
-        <v>643.7953722573419</v>
+        <v>643.7953722573421</v>
       </c>
       <c r="AQ350" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="AR350" s="372" t="n">
         <v>594.4466704358539</v>
       </c>
       <c r="AS350" s="372" t="n">
-        <v>522.2104923178402</v>
+        <v>522.2104923178401</v>
       </c>
       <c r="AT350" s="382" t="n">
         <v>481.682986242403</v>
@@ -68472,16 +68472,16 @@
         <v>15461.55643869437</v>
       </c>
       <c r="BG350" s="386" t="n">
-        <v>643.7953722573419</v>
+        <v>643.7953722573421</v>
       </c>
       <c r="BH350" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="BI350" s="372" t="n">
         <v>594.4466704358539</v>
       </c>
       <c r="BJ350" s="372" t="n">
-        <v>522.2104923178402</v>
+        <v>522.2104923178401</v>
       </c>
       <c r="BK350" s="387" t="n">
         <v>481.682986242403</v>
@@ -68495,7 +68495,7 @@
         <v>61852.87009948627</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>47638.89476372442</v>
+        <v>47638.89476372443</v>
       </c>
       <c r="BU350" s="375" t="n">
         <v>23699.5880807438</v>
@@ -68507,16 +68507,16 @@
         <v>15991.02151431809</v>
       </c>
       <c r="BX350" s="386" t="n">
-        <v>644.4639296475566</v>
+        <v>644.4639296475568</v>
       </c>
       <c r="BY350" s="372" t="n">
-        <v>634.3956583183151</v>
+        <v>634.395658318315</v>
       </c>
       <c r="BZ350" s="372" t="n">
         <v>598.0921575373827</v>
       </c>
       <c r="CA350" s="372" t="n">
-        <v>528.6351855708626</v>
+        <v>528.6351855708625</v>
       </c>
       <c r="CB350" s="387" t="n">
         <v>489.9393772435288</v>
@@ -68671,7 +68671,7 @@
         </is>
       </c>
       <c r="BS351" s="391" t="n">
-        <v>108585.6923770447</v>
+        <v>108585.6923770446</v>
       </c>
       <c r="BT351" s="375" t="n">
         <v>78890.61125065039</v>
@@ -68680,7 +68680,7 @@
         <v>49657.28648921576</v>
       </c>
       <c r="BV351" s="375" t="n">
-        <v>45532.10633539765</v>
+        <v>45532.10633539764</v>
       </c>
       <c r="BW351" s="392" t="n">
         <v>47236.43957443789</v>
@@ -68795,7 +68795,7 @@
         <v>111813.7515740478</v>
       </c>
       <c r="AP352" s="381" t="n">
-        <v>927.1777229284536</v>
+        <v>927.1777229284534</v>
       </c>
       <c r="AQ352" s="372" t="n">
         <v>944.3613432519765</v>
@@ -68807,7 +68807,7 @@
         <v>1026.946673068109</v>
       </c>
       <c r="AT352" s="382" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BA352" s="111" t="inlineStr">
         <is>
@@ -68830,7 +68830,7 @@
         <v>111813.7515740478</v>
       </c>
       <c r="BG352" s="386" t="n">
-        <v>927.1777229284536</v>
+        <v>927.1777229284534</v>
       </c>
       <c r="BH352" s="372" t="n">
         <v>944.3613432519765</v>
@@ -68842,7 +68842,7 @@
         <v>1026.946673068109</v>
       </c>
       <c r="BK352" s="387" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BR352" s="111" t="inlineStr">
         <is>
@@ -68865,7 +68865,7 @@
         <v>112035.7360731496</v>
       </c>
       <c r="BX352" s="386" t="n">
-        <v>927.9148856001563</v>
+        <v>927.914885600156</v>
       </c>
       <c r="BY352" s="372" t="n">
         <v>945.224102043683</v>
@@ -68977,7 +68977,7 @@
         <v>22982.69260371909</v>
       </c>
       <c r="AQ353" s="411" t="n">
-        <v>23249.20816901943</v>
+        <v>23249.20816901942</v>
       </c>
       <c r="AR353" s="411" t="n">
         <v>24684.15169165625</v>
@@ -69012,7 +69012,7 @@
         <v>22982.69260371909</v>
       </c>
       <c r="BH353" s="417" t="n">
-        <v>23249.20816901943</v>
+        <v>23249.20816901942</v>
       </c>
       <c r="BI353" s="417" t="n">
         <v>24684.15169165625</v>
@@ -69032,7 +69032,7 @@
         <v>641442.9563073047</v>
       </c>
       <c r="BT353" s="420" t="n">
-        <v>653579.5666507615</v>
+        <v>653579.5666507614</v>
       </c>
       <c r="BU353" s="420" t="n">
         <v>560122.5913435619</v>
@@ -69047,7 +69047,7 @@
         <v>22981.75510804266</v>
       </c>
       <c r="BY353" s="417" t="n">
-        <v>23244.51211511892</v>
+        <v>23244.51211511891</v>
       </c>
       <c r="BZ353" s="417" t="n">
         <v>24677.77859735915</v>
@@ -69071,7 +69071,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="D354" s="425" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="E354" s="425" t="n">
         <v>719731.1510085932</v>
@@ -69080,19 +69080,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="G354" s="426" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="H354" s="427" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="I354" s="427" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="J354" s="427" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="K354" s="427" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="L354" s="428" t="n">
         <v>3893.954745988455</v>
@@ -69106,7 +69106,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="U354" s="430" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="V354" s="430" t="n">
         <v>719731.1510085932</v>
@@ -69115,19 +69115,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="X354" s="431" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="Y354" s="432" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="Z354" s="433" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="AA354" s="433" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="AB354" s="433" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="AC354" s="434" t="n">
         <v>3893.954745988455</v>
@@ -69162,7 +69162,7 @@
         <v>3693.085197699454</v>
       </c>
       <c r="AS354" s="437" t="n">
-        <v>3688.333869463637</v>
+        <v>3688.333869463638</v>
       </c>
       <c r="AT354" s="438" t="n">
         <v>3876.857014318612</v>
@@ -69197,7 +69197,7 @@
         <v>3693.085197699454</v>
       </c>
       <c r="BJ354" s="443" t="n">
-        <v>3688.333869463637</v>
+        <v>3688.333869463638</v>
       </c>
       <c r="BK354" s="444" t="n">
         <v>3876.857014318612</v>
@@ -69208,10 +69208,10 @@
         </is>
       </c>
       <c r="BS354" s="439" t="n">
-        <v>919942.6178675145</v>
+        <v>919942.6178675144</v>
       </c>
       <c r="BT354" s="440" t="n">
-        <v>884374.613342177</v>
+        <v>884374.6133421769</v>
       </c>
       <c r="BU354" s="440" t="n">
         <v>728128.3309562855</v>
@@ -69223,7 +69223,7 @@
         <v>720938.767404718</v>
       </c>
       <c r="BX354" s="442" t="n">
-        <v>3047.198523892404</v>
+        <v>3047.198523892403</v>
       </c>
       <c r="BY354" s="443" t="n">
         <v>3391.017038221982</v>
@@ -69235,7 +69235,7 @@
         <v>3701.145778726151</v>
       </c>
       <c r="CB354" s="444" t="n">
-        <v>3895.613624687548</v>
+        <v>3895.613624687549</v>
       </c>
       <c r="CI354" s="225" t="n"/>
       <c r="CJ354" s="225" t="n"/>
@@ -71128,16 +71128,16 @@
         <v>15461.55643869437</v>
       </c>
       <c r="AP368" s="381" t="n">
-        <v>643.7953722573419</v>
+        <v>643.7953722573421</v>
       </c>
       <c r="AQ368" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="AR368" s="372" t="n">
         <v>594.4466704358539</v>
       </c>
       <c r="AS368" s="372" t="n">
-        <v>522.2104923178402</v>
+        <v>522.2104923178401</v>
       </c>
       <c r="AT368" s="382" t="n">
         <v>481.682986242403</v>
@@ -71163,16 +71163,16 @@
         <v>15461.55643869437</v>
       </c>
       <c r="BG368" s="386" t="n">
-        <v>643.7953722573419</v>
+        <v>643.7953722573421</v>
       </c>
       <c r="BH368" s="372" t="n">
-        <v>633.1527952982868</v>
+        <v>633.1527952982867</v>
       </c>
       <c r="BI368" s="372" t="n">
         <v>594.4466704358539</v>
       </c>
       <c r="BJ368" s="372" t="n">
-        <v>522.2104923178402</v>
+        <v>522.2104923178401</v>
       </c>
       <c r="BK368" s="387" t="n">
         <v>481.682986242403</v>
@@ -71198,7 +71198,7 @@
         <v>15991.02151431809</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>644.4639296475566</v>
+        <v>644.4639296475568</v>
       </c>
       <c r="BY368" s="372" t="n">
         <v>634.395658318315</v>
@@ -71207,25 +71207,25 @@
         <v>598.0921575373827</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>528.6351855708626</v>
+        <v>528.6351855708625</v>
       </c>
       <c r="CB368" s="387" t="n">
         <v>489.9393772435288</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>470.1326516276238</v>
+        <v>470.1326516276242</v>
       </c>
       <c r="CX368" s="512" t="n">
         <v>447.1539035291418</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>475.8887590734221</v>
+        <v>475.8887590734222</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>501.0331785733998</v>
+        <v>501.0331785734001</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>529.4650756237156</v>
+        <v>529.4650756237161</v>
       </c>
     </row>
     <row r="369">
@@ -71375,7 +71375,7 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>108585.6923770447</v>
+        <v>108585.6923770446</v>
       </c>
       <c r="BT369" s="375" t="n">
         <v>78890.61125065039</v>
@@ -71399,25 +71399,25 @@
         <v>1498.626421398224</v>
       </c>
       <c r="CA369" s="372" t="n">
-        <v>1497.080765601087</v>
+        <v>1497.080765601088</v>
       </c>
       <c r="CB369" s="387" t="n">
         <v>1543.329831986514</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>205.4893311184615</v>
+        <v>205.4893311184614</v>
       </c>
       <c r="CX369" s="375" t="n">
         <v>182.3742328848222</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>197.8808134675973</v>
+        <v>197.8808134675972</v>
       </c>
       <c r="CZ369" s="375" t="n">
         <v>215.3422933043807</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>199.1713198083629</v>
+        <v>199.171319808363</v>
       </c>
     </row>
     <row r="370">
@@ -71512,7 +71512,7 @@
         <v>111813.7515740478</v>
       </c>
       <c r="AP370" s="381" t="n">
-        <v>927.1777229284536</v>
+        <v>927.1777229284534</v>
       </c>
       <c r="AQ370" s="372" t="n">
         <v>944.3613432519765</v>
@@ -71524,7 +71524,7 @@
         <v>1026.946673068109</v>
       </c>
       <c r="AT370" s="382" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BA370" s="111" t="inlineStr">
         <is>
@@ -71547,7 +71547,7 @@
         <v>111813.7515740478</v>
       </c>
       <c r="BG370" s="386" t="n">
-        <v>927.1777229284536</v>
+        <v>927.1777229284534</v>
       </c>
       <c r="BH370" s="372" t="n">
         <v>944.3613432519765</v>
@@ -71559,7 +71559,7 @@
         <v>1026.946673068109</v>
       </c>
       <c r="BK370" s="387" t="n">
-        <v>1104.86056866744</v>
+        <v>1104.860568667439</v>
       </c>
       <c r="BR370" s="111" t="inlineStr">
         <is>
@@ -71582,7 +71582,7 @@
         <v>112035.7360731496</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>927.9148856001563</v>
+        <v>927.914885600156</v>
       </c>
       <c r="BY370" s="372" t="n">
         <v>945.224102043683</v>
@@ -71597,16 +71597,16 @@
         <v>1106.234747132765</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>155.7444826987016</v>
+        <v>155.7444826987017</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>166.7242340633323</v>
+        <v>166.7242340633324</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>181.5686690783151</v>
+        <v>181.568669078315</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>207.8100403343034</v>
+        <v>207.8100403343033</v>
       </c>
       <c r="DA370" s="392" t="n">
         <v>221.9844991017722</v>
@@ -71707,7 +71707,7 @@
         <v>22982.69260371909</v>
       </c>
       <c r="AQ371" s="411" t="n">
-        <v>23249.20816901943</v>
+        <v>23249.20816901942</v>
       </c>
       <c r="AR371" s="411" t="n">
         <v>24684.15169165625</v>
@@ -71742,7 +71742,7 @@
         <v>22982.69260371909</v>
       </c>
       <c r="BH371" s="417" t="n">
-        <v>23249.20816901943</v>
+        <v>23249.20816901942</v>
       </c>
       <c r="BI371" s="417" t="n">
         <v>24684.15169165625</v>
@@ -71762,7 +71762,7 @@
         <v>641442.9563073047</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>653579.5666507615</v>
+        <v>653579.5666507614</v>
       </c>
       <c r="BU371" s="420" t="n">
         <v>560122.5913435619</v>
@@ -71777,7 +71777,7 @@
         <v>22981.75510804266</v>
       </c>
       <c r="BY371" s="417" t="n">
-        <v>23244.51211511892</v>
+        <v>23244.51211511891</v>
       </c>
       <c r="BZ371" s="417" t="n">
         <v>24677.77859735915</v>
@@ -71789,19 +71789,19 @@
         <v>26563.90922540538</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>117.1118582179326</v>
+        <v>117.1118582179284</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>16.66360952908172</v>
+        <v>16.6636095290815</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>18.02851745380418</v>
+        <v>18.02851745380356</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>19.31384257715574</v>
+        <v>19.3138425771552</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>20.69080366985125</v>
+        <v>20.69080366985056</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71814,7 +71814,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="D372" s="425" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="E372" s="425" t="n">
         <v>719731.1510085932</v>
@@ -71823,19 +71823,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="G372" s="426" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="H372" s="427" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="I372" s="427" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="J372" s="427" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="K372" s="427" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="L372" s="428" t="n">
         <v>3893.954745988455</v>
@@ -71849,7 +71849,7 @@
         <v>914173.6105900046</v>
       </c>
       <c r="U372" s="430" t="n">
-        <v>877022.092101255</v>
+        <v>877022.0921012548</v>
       </c>
       <c r="V372" s="430" t="n">
         <v>719731.1510085932</v>
@@ -71858,19 +71858,19 @@
         <v>676839.4227001966</v>
       </c>
       <c r="X372" s="431" t="n">
-        <v>711031.5138816028</v>
+        <v>711031.5138816027</v>
       </c>
       <c r="Y372" s="432" t="n">
         <v>3049.699233174204</v>
       </c>
       <c r="Z372" s="433" t="n">
-        <v>3395.734214293859</v>
+        <v>3395.734214293858</v>
       </c>
       <c r="AA372" s="433" t="n">
         <v>3705.423537142854</v>
       </c>
       <c r="AB372" s="433" t="n">
-        <v>3702.55515048157</v>
+        <v>3702.555150481571</v>
       </c>
       <c r="AC372" s="434" t="n">
         <v>3893.954745988455</v>
@@ -71905,7 +71905,7 @@
         <v>3693.085197699454</v>
       </c>
       <c r="AS372" s="437" t="n">
-        <v>3688.333869463637</v>
+        <v>3688.333869463638</v>
       </c>
       <c r="AT372" s="438" t="n">
         <v>3876.857014318612</v>
@@ -71940,7 +71940,7 @@
         <v>3693.085197699454</v>
       </c>
       <c r="BJ372" s="443" t="n">
-        <v>3688.333869463637</v>
+        <v>3688.333869463638</v>
       </c>
       <c r="BK372" s="444" t="n">
         <v>3876.857014318612</v>
@@ -71951,10 +71951,10 @@
         </is>
       </c>
       <c r="BS372" s="439" t="n">
-        <v>919942.6178675145</v>
+        <v>919942.6178675144</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>884374.613342177</v>
+        <v>884374.6133421769</v>
       </c>
       <c r="BU372" s="440" t="n">
         <v>728128.3309562855</v>
@@ -71966,7 +71966,7 @@
         <v>720938.7674047179</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3047.198523892404</v>
+        <v>3047.198523892403</v>
       </c>
       <c r="BY372" s="443" t="n">
         <v>3391.017038221983</v>
@@ -71981,19 +71981,19 @@
         <v>3895.613624687548</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>948.4783236627195</v>
+        <v>948.4783236627156</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>812.915980006378</v>
+        <v>812.9159800063778</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>873.3667590731386</v>
+        <v>873.3667590731379</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>943.4993547892396</v>
+        <v>943.4993547892393</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>971.311698203702</v>
+        <v>971.3116982037019</v>
       </c>
     </row>
     <row r="375">
